--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.1%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>441.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-608.9%</t>
+          <t>-590.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>46.5%</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>-2.2%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>46.8%</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.1%</t>
+          <t>-83.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.1%</t>
+          <t>-252.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.0%</t>
+          <t>-159.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.9%</t>
+          <t>-257.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,37 +1461,37 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-203.0%</t>
+          <t>-170.9%</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -46122,19 +46122,19 @@
         <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>3.031299837586259</v>
       </c>
       <c r="D1938" t="n">
         <v>-4.655977015541577</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9597186129206214</v>
+        <v>1.168552607055881</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3790843848755552</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.595015212525666</v>
+        <v>2.803849206660926</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>3.035867069578047</v>
       </c>
       <c r="D1939" t="n">
         <v>-4.480502755749107</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.034475548829397</v>
+        <v>1.243309542964656</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3790843848755552</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.599582444517454</v>
+        <v>2.808416438652714</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.827044549329585</v>
+        <v>3.035878543464844</v>
       </c>
       <c r="D1940" t="n">
         <v>-4.591439008390356</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9901125216596951</v>
+        <v>1.198946515794954</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3790843848755552</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.599593918404252</v>
+        <v>2.808427912539511</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.83017593454949</v>
+        <v>3.03900992868475</v>
       </c>
       <c r="D1941" t="n">
         <v>-4.794465585933589</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9120332758623073</v>
+        <v>1.120867269997567</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.5821109624187886</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.480909357098217</v>
+        <v>2.689743351233477</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.840348320981623</v>
+        <v>3.049182315116882</v>
       </c>
       <c r="D1942" t="n">
         <v>-4.636539986998296</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9853759018685568</v>
+        <v>1.194209896003816</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.5821109624187886</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.49108174353035</v>
+        <v>2.699915737665609</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.835294591555483</v>
+        <v>3.044128585690742</v>
       </c>
       <c r="D1943" t="n">
         <v>-4.784861240809425</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9209936709179658</v>
+        <v>1.129827665053225</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.5821109624187886</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.48602801410421</v>
+        <v>2.694862008239469</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.827070367000009</v>
+        <v>3.035904361135268</v>
       </c>
       <c r="D1944" t="n">
         <v>-4.786044325460486</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.912296212502067</v>
+        <v>1.121130206637326</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.5877540108853001</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.474417960468829</v>
+        <v>2.683251954604088</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.82762224003311</v>
+        <v>3.036456234168369</v>
       </c>
       <c r="D1945" t="n">
         <v>-4.662916618466403</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9620991683328017</v>
+        <v>1.170933162468061</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.5877540108853001</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.47496983350193</v>
+        <v>2.68380382763719</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.756894931924476</v>
+        <v>2.965728926059735</v>
       </c>
       <c r="D1946" t="n">
         <v>-4.570106137015543</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9284960528045114</v>
+        <v>1.137330046939771</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.4949435294344408</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.459928814263812</v>
+        <v>2.668762808399071</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.758768407849077</v>
+        <v>2.967602401984336</v>
       </c>
       <c r="D1947" t="n">
         <v>-4.521543084794513</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9497947496175241</v>
+        <v>1.158628743752783</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4463804772134106</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.490940121521031</v>
+        <v>2.69977411565629</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.7538441163608</v>
+        <v>2.962678110496059</v>
       </c>
       <c r="D1948" t="n">
         <v>-4.408871866558263</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9899389454237473</v>
+        <v>1.198772939559007</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3337092589771604</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.553618560974503</v>
+        <v>2.762452555109763</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.759335412191467</v>
+        <v>2.968169406326726</v>
       </c>
       <c r="D1949" t="n">
         <v>-4.29649486537559</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.040381041727484</v>
+        <v>1.249215035862743</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3337092589771604</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.559109856805171</v>
+        <v>2.76794385094043</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.770832613960006</v>
+        <v>2.979666608095265</v>
       </c>
       <c r="D1950" t="n">
         <v>-4.494729434262321</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9725844159413304</v>
+        <v>1.18141841007659</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5319438278638909</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.451666317241671</v>
+        <v>2.660500311376931</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.609188333960659</v>
+        <v>2.818022328095918</v>
       </c>
       <c r="D1951" t="n">
         <v>-4.5777307152876</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7777396235318721</v>
+        <v>0.9865736176671314</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5505147123910648</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.278879506526021</v>
+        <v>2.48771350066128</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.729337994679865</v>
+        <v>2.938171988815124</v>
       </c>
       <c r="D1952" t="n">
         <v>-4.418536443231023</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9615669930737083</v>
+        <v>1.170400987208968</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5505147123910648</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.399029167245226</v>
+        <v>2.607863161380485</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.743851020782188</v>
+        <v>2.952685014917447</v>
       </c>
       <c r="D1953" t="n">
         <v>-4.505135026212126</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9414405859835902</v>
+        <v>1.150274580118849</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5505147123910648</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.413542193347549</v>
+        <v>2.622376187482808</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.743450004618746</v>
+        <v>3.417612844998823</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.741270462124556</v>
+        <v>2.950104456259816</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.473400056281783</v>
+        <v>-4.285637743490835</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9515540152980959</v>
+        <v>1.235492934549735</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.518779742460722</v>
+        <v>-0.3310174296697733</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.430002616648124</v>
+        <v>2.751493998457952</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-37.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>115.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>135.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-693.6%</t>
+          <t>-696.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-57.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.2%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-590.1%</t>
+          <t>-611.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-279.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>4.6%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>46.5%</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>-2.4%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>46.9%</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-83.6%</t>
+          <t>-94.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-252.7%</t>
+          <t>-282.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-317.8%</t>
+          <t>-320.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-36.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.4%</t>
+          <t>-155.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.1%</t>
+          <t>-278.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-191.1%</t>
+          <t>-192.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,37 +1461,37 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-28.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.9%</t>
+          <t>-204.3%</t>
         </is>
       </c>
     </row>
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.319973263478165</v>
+        <v>-5.352397647260032</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9840105793278613</v>
+        <v>0.9710408258151144</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9380883224177073</v>
+        <v>-0.9655826024852492</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.549503315582251</v>
+        <v>2.533006747541725</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.655635910708617</v>
+        <v>-5.688060294490485</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8483261120916454</v>
+        <v>0.8353563585788986</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9380883224177073</v>
+        <v>-0.9655826024852492</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.548083907238215</v>
+        <v>2.53158733919769</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.019262155608931</v>
+        <v>-6.051686539390798</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7093631743657616</v>
+        <v>0.6963934208530147</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.036309959284833</v>
+        <v>-1.063804239352375</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.495638485352182</v>
+        <v>2.479141917311657</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.384389538247677</v>
+        <v>-6.416813922029545</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5625667363160942</v>
+        <v>0.5495969828033473</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.332620743583846</v>
+        <v>-1.360115023651387</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.317106529778606</v>
+        <v>2.30060996173808</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.792978315428355</v>
+        <v>-6.825402699210223</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3978927694585823</v>
+        <v>0.3849230159458354</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.768703800832066</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.070714807484958</v>
+        <v>2.054218239444432</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.205960799569449</v>
+        <v>-7.238385183351316</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2278852082736051</v>
+        <v>0.2149154547608583</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.768703800832066</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.065900239956418</v>
+        <v>2.049403671915893</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.622352673856446</v>
+        <v>-7.654777057638314</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05932250916768389</v>
+        <v>0.04635275565493657</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.768703800832066</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063894290565296</v>
+        <v>2.04739772252477</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-8.031454068168157</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.09405935788832176</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.768703800832066</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.074152981233975</v>
+        <v>2.057656413193449</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.377328890152967</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.2363097215365504</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.768703800832066</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.070252546379669</v>
+        <v>2.053755978339145</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.53947116061606</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.3027617096667865</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.768703800832066</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.06865746643467</v>
+        <v>2.052160898394146</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.836132502426258</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.4176472704616576</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.837446936565944</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031190560923552</v>
+        <v>2.014693992883027</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.269481610536493</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5950132182401546</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.837446936565944</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027164256389149</v>
+        <v>2.010667688348623</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.652482999279124</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.7483158750587915</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.837446936565944</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027062155067564</v>
+        <v>2.010565587027039</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.809881879492245</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.8087039111726093</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.994845816779066</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>1.918697774870597</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.16941220199625</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.9471657368761601</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.994845816779066</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>1.924048078168647</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.49581223066126</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.069809728384988</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.321245845444079</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.736124080926817</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.71496119873546</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.154427564992897</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.540394813518276</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.607676450704067</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.71127027377905</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.152951195010333</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.540394813518276</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.607676450704067</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.91552844910891</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.229141268023636</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.668033758132265</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.536606281054316</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-11.13356622074009</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.311873822191672</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.842804526228164</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.436226374681213</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-11.06009638907264</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.267114188031271</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.769334694560715</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.495679975175103</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.23522080645918</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.322608734238371</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.944459111947259</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.405160545490694</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.46967290047367</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.423608736745763</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.944459111947259</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.397941380589098</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.75747674501091</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.545402465334635</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.232262956484497</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.218586883092779</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.98730119217474</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.636216454361609</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.394910493554658</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.122114150689239</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.219330111911</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.726334293626999</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.456923190743081</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.087600261005299</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.16731459794218</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.701537752353072</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.456923190743081</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.0915905966917</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.3089864396663</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.759681715941462</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.456923190743081</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.090115369792958</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.25939559524147</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.724791968006656</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.407332346318247</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.134923286612731</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-12.06024348800437</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.6581822587585</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.242009820368434</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.221065668535936</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.83439833528496</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.558265124634527</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.20008314478127</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.255800746924443</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.70981967894737</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.507294517543431</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.20008314478127</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.256939891480502</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.76271496699165</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.525818858599037</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.195127798692824</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.262546873295677</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.4788062360629</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.406521661988902</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.195127798692824</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.268280577534314</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.40743984345326</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.387712367338908</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.123761406083176</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.317859718746762</v>
+        <v>1.301363150706237</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-11.14360297624919</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.292061101770188</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.123761406083176</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.307976237433855</v>
+        <v>1.291479669393329</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84393679159892</v>
+        <v>-10.87636117538079</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174029188409456</v>
+        <v>-1.186998941922202</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.123761406083176</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.306141676934481</v>
+        <v>1.289645108893956</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.72063086312071</v>
+        <v>-10.75305524690257</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.125007131991629</v>
+        <v>-1.137976885504375</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.006849454888072</v>
+        <v>-3.034343734955614</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.359491964637558</v>
+        <v>1.342995396597032</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.69667732214475</v>
+        <v>-10.72910170592661</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.114757209455753</v>
+        <v>-1.127726962968498</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.982895913912114</v>
+        <v>-3.010390193979656</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.374532595368626</v>
+        <v>1.3580360273281</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.43261738382195</v>
+        <v>-10.46504176760382</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.022393550288386</v>
+        <v>-1.035363303801132</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.74633025565686</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.519708242200551</v>
+        <v>1.503211674160026</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.725537760317113</v>
+        <v>-9.757962144098979</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7423487345467517</v>
+        <v>-0.7553184880594981</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.74633025565686</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.516921208540251</v>
+        <v>1.500424640499725</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.685353461950923</v>
+        <v>-9.717777845732789</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7259313913124341</v>
+        <v>-0.7389011448251805</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.678651677223127</v>
+        <v>-2.706145957290669</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.541375411447807</v>
+        <v>1.524878843407281</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.605283666413118</v>
+        <v>-9.637708050194984</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6945366518765557</v>
+        <v>-0.7075064053893017</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.598581881685323</v>
+        <v>-2.626076161752865</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.588784109991246</v>
+        <v>1.572287541950721</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.371802444183519</v>
+        <v>-9.404226827965385</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5932197341468632</v>
+        <v>-0.6061894876596097</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.365100659455724</v>
+        <v>-2.392594939523267</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.736797272166857</v>
+        <v>1.720300704126332</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.192093914039646</v>
+        <v>-9.224518297821511</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5242285324022733</v>
+        <v>-0.5371982859150193</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.307929155293028</v>
+        <v>-2.335423435360571</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.768207964351516</v>
+        <v>1.75171139631099</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.059818440408758</v>
+        <v>-9.092242824190624</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4759508562028913</v>
+        <v>-0.4889206097156373</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.175653681662142</v>
+        <v>-2.203147961729684</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.842940735277075</v>
+        <v>1.826444167236549</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.869218765735605</v>
+        <v>-8.90164314951747</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.396895925645993</v>
+        <v>-0.4098656791587394</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.985054006988989</v>
+        <v>-2.012548287056532</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.960115600768603</v>
+        <v>1.943619032728078</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.620218967052024</v>
+        <v>-8.652643350833889</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2843896649489017</v>
+        <v>-0.2973594184616482</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.985054006988989</v>
+        <v>-2.012548287056532</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.973021941992262</v>
+        <v>1.956525373951736</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.725808956825128</v>
+        <v>-8.758233340606994</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4546015904573624</v>
+        <v>-0.4675713439701088</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.118138276829636</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.781692018529181</v>
+        <v>1.765195450488655</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.744543858943725</v>
+        <v>-8.776968242725591</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4135512094277147</v>
+        <v>-0.4265209629404612</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.118138276829636</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.830236360406267</v>
+        <v>1.813739792365741</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.596603817536126</v>
+        <v>-8.629028201317992</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4742541155528426</v>
+        <v>-0.487223869065589</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.070323080853536</v>
+        <v>-2.097817360921078</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.722549987263234</v>
+        <v>1.706053419222708</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.572375181147153</v>
+        <v>-8.604799564929019</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4732766472507319</v>
+        <v>-0.4862464007634779</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.073588724532106</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.728373182843139</v>
+        <v>1.711876614802613</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.528826774376462</v>
+        <v>-8.561251158158328</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4628178966375485</v>
+        <v>-0.4757876501502949</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.073588724532106</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.721412570748046</v>
+        <v>1.70491600270752</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.286678380922604</v>
+        <v>-8.31910276470447</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3514961848748621</v>
+        <v>-0.3644659383876085</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.073588724532106</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.735874925129189</v>
+        <v>1.719378357088663</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.223449009154256</v>
+        <v>-8.255873392936122</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3316723157083281</v>
+        <v>-0.3446420692210745</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.073588724532106</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.730407045588384</v>
+        <v>1.713910477547858</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.100157874337127</v>
+        <v>-8.132582258118992</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2848577677708994</v>
+        <v>-0.2978275212836454</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.922803309647434</v>
+        <v>-1.950297589714976</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.801879820489239</v>
+        <v>1.785383252448713</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.079008675433684</v>
+        <v>-8.11143305921555</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2686971099721971</v>
+        <v>-0.2816668634849435</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.929148390811533</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.82227031806863</v>
+        <v>1.805773750028105</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.83524323345024</v>
+        <v>-7.867667617232105</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1754102248317686</v>
+        <v>-0.188379978344515</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.929148390811533</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.818051026415681</v>
+        <v>1.801554458375155</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.57121516625698</v>
+        <v>-7.603639550038846</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.06767468403444887</v>
+        <v>-0.0806444375471953</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.727282991995579</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.941294579625269</v>
+        <v>1.924798011584743</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.321364772307906</v>
+        <v>-7.353789156089771</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.02500754852888321</v>
+        <v>0.01203779501613678</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.727282991995579</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.934036654608971</v>
+        <v>1.917540086568446</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.145472679840474</v>
+        <v>-7.177897063622339</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.09896350903650486</v>
+        <v>0.08599375552375843</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.727282991995579</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.93763577812962</v>
+        <v>1.921139210089094</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.97402621681801</v>
+        <v>-7.006450600599876</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1808696003000438</v>
+        <v>0.1678998467872974</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528342248905573</v>
+        <v>-1.555836528973116</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.053831161997651</v>
+        <v>2.037334593957126</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.748993217149187</v>
+        <v>-6.781417600931053</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2699032777838699</v>
+        <v>0.2569335242711235</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.30330924923675</v>
+        <v>-1.330803529304293</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.187871439415242</v>
+        <v>2.171374871374717</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.53435883951278</v>
+        <v>-6.566783223294646</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3604518298927499</v>
+        <v>0.3474820763800035</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.116169151667886</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.321346867051404</v>
+        <v>2.304850299010878</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.267758482538428</v>
+        <v>-6.300182866320294</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4482862314662861</v>
+        <v>0.4353164779535401</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.116169151667886</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.302541125835199</v>
+        <v>2.286044557794674</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.027327985733568</v>
+        <v>-6.059752369515434</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5462015068131079</v>
+        <v>0.5332317533003614</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.8757386548630257</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.448542500542993</v>
+        <v>2.432045932502467</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.784537178084123</v>
+        <v>-5.816961561865988</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6472471437077063</v>
+        <v>0.6342773901949599</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.8757386548630257</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.452471814377813</v>
+        <v>2.435975246337287</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.668597328458937</v>
+        <v>-5.701021712240803</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6943016674751203</v>
+        <v>0.6813319139623739</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.7989169238469018</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.499243436904827</v>
+        <v>2.482746868864302</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.425941740035775</v>
+        <v>-5.45836612381764</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.788361974064379</v>
+        <v>0.7753922205516326</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.7989169238469018</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.496241508124821</v>
+        <v>2.479744940084295</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.205920941998764</v>
+        <v>-5.23834532578063</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8779493302897974</v>
+        <v>0.864979576777051</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.6576970787789216</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.582552452176223</v>
+        <v>2.566055884135698</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.006672312093955</v>
+        <v>-5.039096695875821</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9735429650535443</v>
+        <v>0.9605732115407979</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.6576970787789216</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.598446634978046</v>
+        <v>2.581950066937521</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.847157208574585</v>
+        <v>-4.879581592356451</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.038494850901594</v>
+        <v>1.025525097388848</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4706876951920093</v>
+        <v>-0.4981819752595517</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.69530154152997</v>
+        <v>2.678804973489445</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.702485063474848</v>
+        <v>-4.734909447256713</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.106451811502929</v>
+        <v>1.093482057990183</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3260155500922718</v>
+        <v>-0.3535098301598142</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.792192931151253</v>
+        <v>2.775696363110727</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.76235989083254</v>
+        <v>-4.794784274614406</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.068539371961278</v>
+        <v>1.055569618448531</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.4133846575175064</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.742305526138063</v>
+        <v>2.725808958097538</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.675560393053532</v>
+        <v>-4.707984776835398</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.125659664395447</v>
+        <v>1.112689910882701</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.4133846575175064</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.764706019460629</v>
+        <v>2.748209451420104</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.678030099515338</v>
+        <v>-4.710454483297204</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.124744183184137</v>
+        <v>1.111774429671391</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3883600839117701</v>
+        <v>-0.4158543639793125</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.763296596956958</v>
+        <v>2.746800028916432</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.746400285839348</v>
+        <v>-4.778824669621214</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.108403031129235</v>
+        <v>1.095433277616489</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4065786649430976</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.779868938853388</v>
+        <v>2.763372370812863</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.624983856212872</v>
+        <v>-4.657408239994737</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.147406311611717</v>
+        <v>1.134436558098971</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4065786649430976</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.77030564748528</v>
+        <v>2.753809079444754</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.031299837586259</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.655977015541577</v>
+        <v>-4.688401399323443</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.168552607055881</v>
+        <v>0.9467488594078752</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4065786649430976</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.803849206660926</v>
+        <v>2.578518644485141</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.035867069578047</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.480502755749107</v>
+        <v>-4.512927139530973</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.243309542964656</v>
+        <v>1.021505795316651</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4065786649430976</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.808416438652714</v>
+        <v>2.583085876476929</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.035878543464844</v>
+        <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.591439008390356</v>
+        <v>-4.623863392172222</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.198946515794954</v>
+        <v>0.9771427681469489</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4065786649430976</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.808427912539511</v>
+        <v>2.583097350363726</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.03900992868475</v>
+        <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.794465585933589</v>
+        <v>-4.826889969715455</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.120867269997567</v>
+        <v>0.8990635223495611</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.609605242486331</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.689743351233477</v>
+        <v>2.464412789057692</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.049182315116882</v>
+        <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.636539986998296</v>
+        <v>-4.668964370780162</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.194209896003816</v>
+        <v>0.9724061483558106</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.609605242486331</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.699915737665609</v>
+        <v>2.474585175489824</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.044128585690742</v>
+        <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.784861240809425</v>
+        <v>-4.817285624591291</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.129827665053225</v>
+        <v>0.9080239174052194</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.609605242486331</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.694862008239469</v>
+        <v>2.469531446063685</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.035904361135268</v>
+        <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.786044325460486</v>
+        <v>-4.818468709242351</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.121130206637326</v>
+        <v>0.8993264589893208</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.6152482909528425</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.683251954604088</v>
+        <v>2.457921392428303</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.036456234168369</v>
+        <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.662916618466403</v>
+        <v>-4.695341002248268</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.170933162468061</v>
+        <v>0.9491294148200555</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.6152482909528425</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.68380382763719</v>
+        <v>2.458473265461405</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.965728926059735</v>
+        <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.570106137015543</v>
+        <v>-4.602530520797409</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.137330046939771</v>
+        <v>0.915526299291765</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4949435294344408</v>
+        <v>-0.5224378095019832</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.668762808399071</v>
+        <v>2.443432246223286</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.967602401984336</v>
+        <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.521543084794513</v>
+        <v>-4.553967468576379</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.158628743752783</v>
+        <v>0.9368249961047779</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4463804772134106</v>
+        <v>-0.473874757280953</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.69977411565629</v>
+        <v>2.474443553480505</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.962678110496059</v>
+        <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.408871866558263</v>
+        <v>-4.441296250340129</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.198772939559007</v>
+        <v>0.9769691919110008</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.3612035390447028</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.762452555109763</v>
+        <v>2.537121992933978</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.968169406326726</v>
+        <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.29649486537559</v>
+        <v>-4.328919249157456</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.249215035862743</v>
+        <v>1.027411288214737</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.3612035390447028</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.76794385094043</v>
+        <v>2.542613288764645</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.979666608095265</v>
+        <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.494729434262321</v>
+        <v>-4.527153818044186</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.18141841007659</v>
+        <v>0.9596146624285842</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5319438278638909</v>
+        <v>-0.5594381079314333</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.660500311376931</v>
+        <v>2.435169749201146</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.818022328095918</v>
+        <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.5777307152876</v>
+        <v>-4.610155099069465</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9865736176671314</v>
+        <v>0.7647698700191259</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.5780089924586072</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.48771350066128</v>
+        <v>2.262382938485495</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.938171988815124</v>
+        <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.418536443231023</v>
+        <v>-4.450960827012889</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.170400987208968</v>
+        <v>0.9485972395609621</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.5780089924586072</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.607863161380485</v>
+        <v>2.382532599204701</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.952685014917447</v>
+        <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.505135026212126</v>
+        <v>-4.537559409993992</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.150274580118849</v>
+        <v>0.9284708324708439</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.5780089924586072</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.622376187482808</v>
+        <v>2.397045625307024</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.417612844998823</v>
+        <v>3.745014477547768</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.950104456259816</v>
+        <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.285637743490835</v>
+        <v>-4.49917574743584</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.235492934549735</v>
+        <v>0.9412437388364729</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3310174296697733</v>
+        <v>-0.539625329900456</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.751493998457952</v>
+        <v>2.417495264184283</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.5%</t>
+          <t>115.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.7%</t>
+          <t>135.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-696.8%</t>
+          <t>-693.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.1%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.5%</t>
+          <t>-601.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-279.1%</t>
+          <t>-277.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-94.1%</t>
+          <t>-84.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.1%</t>
+          <t>-278.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-320.6%</t>
+          <t>-317.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.4%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-278.0%</t>
+          <t>-275.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-192.7%</t>
+          <t>-191.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-204.3%</t>
+          <t>-202.6%</t>
         </is>
       </c>
     </row>
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.352397647260032</v>
+        <v>-5.319973263478165</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9710408258151144</v>
+        <v>0.9840105793278613</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9655826024852492</v>
+        <v>-0.9380883224177073</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.533006747541725</v>
+        <v>2.549503315582251</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.688060294490485</v>
+        <v>-5.655635910708617</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8353563585788986</v>
+        <v>0.8483261120916454</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9655826024852492</v>
+        <v>-0.9380883224177073</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.53158733919769</v>
+        <v>2.548083907238215</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.051686539390798</v>
+        <v>-6.019262155608931</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6963934208530147</v>
+        <v>0.7093631743657616</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.063804239352375</v>
+        <v>-1.036309959284833</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.479141917311657</v>
+        <v>2.495638485352182</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.416813922029545</v>
+        <v>-6.384389538247677</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5495969828033473</v>
+        <v>0.5625667363160942</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.360115023651387</v>
+        <v>-1.332620743583846</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.30060996173808</v>
+        <v>2.317106529778606</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.825402699210223</v>
+        <v>-6.792978315428355</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3849230159458354</v>
+        <v>0.3978927694585823</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.768703800832066</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.054218239444432</v>
+        <v>2.070714807484958</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.238385183351316</v>
+        <v>-7.205960799569449</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2149154547608583</v>
+        <v>0.2278852082736051</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.768703800832066</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.049403671915893</v>
+        <v>2.065900239956418</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.654777057638314</v>
+        <v>-7.622352673856446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.04635275565493657</v>
+        <v>0.05932250916768389</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.768703800832066</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.04739772252477</v>
+        <v>2.063894290565296</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.031454068168157</v>
+        <v>-7.999029684386291</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.09405935788832176</v>
+        <v>-0.08108960437557489</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.768703800832066</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.057656413193449</v>
+        <v>2.074152981233975</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.377328890152967</v>
+        <v>-8.344904506371099</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2363097215365504</v>
+        <v>-0.2233399680238031</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.768703800832066</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.053755978339145</v>
+        <v>2.070252546379669</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.53947116061606</v>
+        <v>-8.507046776834192</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3027617096667865</v>
+        <v>-0.2897919561540396</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.768703800832066</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.052160898394146</v>
+        <v>2.06865746643467</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.836132502426258</v>
+        <v>-8.803708118644391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4176472704616576</v>
+        <v>-0.4046775169489107</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.837446936565944</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.014693992883027</v>
+        <v>2.031190560923552</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.269481610536493</v>
+        <v>-9.237057226754626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5950132182401546</v>
+        <v>-0.5820434647274078</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.837446936565944</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.010667688348623</v>
+        <v>2.027164256389149</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.652482999279124</v>
+        <v>-9.620058615497257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7483158750587915</v>
+        <v>-0.7353461215460442</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.837446936565944</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.010565587027039</v>
+        <v>2.027062155067564</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.809881879492245</v>
+        <v>-9.777457495710378</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8087039111726093</v>
+        <v>-0.7957341576598624</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.994845816779066</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.918697774870597</v>
+        <v>1.935194342911122</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.16941220199625</v>
+        <v>-10.13698781821438</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9471657368761601</v>
+        <v>-0.9341959833634128</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.994845816779066</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.924048078168647</v>
+        <v>1.940544646209172</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.49581223066126</v>
+        <v>-10.46338784687939</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.069809728384988</v>
+        <v>-1.05683997487224</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.321245845444079</v>
+        <v>-2.293751565376537</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.736124080926817</v>
+        <v>1.752620648967342</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.71496119873546</v>
+        <v>-10.68253681495359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.154427564992897</v>
+        <v>-1.141457811480151</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.540394813518276</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.607676450704067</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.71127027377905</v>
+        <v>-10.67884588999718</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.152951195010333</v>
+        <v>-1.139981441497586</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.540394813518276</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.607676450704067</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.91552844910891</v>
+        <v>-10.88310406532704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.229141268023636</v>
+        <v>-1.21617151451089</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.668033758132265</v>
+        <v>-2.640539478064723</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.536606281054316</v>
+        <v>1.553102849094841</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.13356622074009</v>
+        <v>-11.10114183695822</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.311873822191672</v>
+        <v>-1.298904068678925</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.842804526228164</v>
+        <v>-2.815310246160622</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.436226374681213</v>
+        <v>1.452722942721738</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.06009638907264</v>
+        <v>-11.02767200529077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.267114188031271</v>
+        <v>-1.254144434518524</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.769334694560715</v>
+        <v>-2.741840414493173</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.495679975175103</v>
+        <v>1.512176543215628</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.23522080645918</v>
+        <v>-11.20279642267731</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.322608734238371</v>
+        <v>-1.309638980725625</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.944459111947259</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.405160545490694</v>
+        <v>1.421657113531219</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.46967290047367</v>
+        <v>-11.4372485166918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.423608736745763</v>
+        <v>-1.410638983233016</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.944459111947259</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.397941380589098</v>
+        <v>1.414437948629623</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.75747674501091</v>
+        <v>-11.72505236122904</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.545402465334635</v>
+        <v>-1.532432711821888</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.232262956484497</v>
+        <v>-3.204768676416955</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.218586883092779</v>
+        <v>1.235083451133304</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.98730119217474</v>
+        <v>-11.95487680839287</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.636216454361609</v>
+        <v>-1.623246700848862</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.394910493554658</v>
+        <v>-3.367416213487116</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.122114150689239</v>
+        <v>1.138610718729764</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.219330111911</v>
+        <v>-12.18690572812913</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.726334293626999</v>
+        <v>-1.713364540114252</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.456923190743081</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.087600261005299</v>
+        <v>1.104096829045825</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.16731459794218</v>
+        <v>-12.13489021416032</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.701537752353072</v>
+        <v>-1.688567998840326</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.456923190743081</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.0915905966917</v>
+        <v>1.108087164732225</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.3089864396663</v>
+        <v>-12.27656205588444</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.759681715941462</v>
+        <v>-1.746711962428716</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.456923190743081</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.090115369792958</v>
+        <v>1.106611937833484</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.25939559524147</v>
+        <v>-12.2269712114596</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.724791968006656</v>
+        <v>-1.71182221449391</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.407332346318247</v>
+        <v>-3.379838066250705</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.134923286612731</v>
+        <v>1.151419854653256</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.06024348800437</v>
+        <v>-12.0278191042225</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.6581822587585</v>
+        <v>-1.645212505245753</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.242009820368434</v>
+        <v>-3.214515540300892</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.221065668535936</v>
+        <v>1.237562236576461</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.83439833528496</v>
+        <v>-11.80197395150309</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.558265124634527</v>
+        <v>-1.54529537112178</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.20008314478127</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.255800746924443</v>
+        <v>1.272297314964968</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.70981967894737</v>
+        <v>-11.6773952951655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.507294517543431</v>
+        <v>-1.494324764030684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.20008314478127</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.256939891480502</v>
+        <v>1.273436459521027</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.76271496699165</v>
+        <v>-11.73029058320979</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.525818858599037</v>
+        <v>-1.512849105086292</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.195127798692824</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.262546873295677</v>
+        <v>1.279043441336202</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.4788062360629</v>
+        <v>-11.44638185228104</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.406521661988902</v>
+        <v>-1.393551908476155</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.195127798692824</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.268280577534314</v>
+        <v>1.284777145574839</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.40743984345326</v>
+        <v>-11.37501545967139</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.387712367338908</v>
+        <v>-1.374742613826162</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.123761406083176</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.301363150706237</v>
+        <v>1.317859718746762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14360297624919</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.292061101770188</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.123761406083176</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.291479669393329</v>
+        <v>1.307976237433855</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87636117538079</v>
+        <v>-10.84393679159892</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.186998941922202</v>
+        <v>-1.174029188409456</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.123761406083176</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.289645108893956</v>
+        <v>1.306141676934481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.75305524690257</v>
+        <v>-10.72063086312071</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.137976885504375</v>
+        <v>-1.125007131991629</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.034343734955614</v>
+        <v>-3.006849454888072</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.342995396597032</v>
+        <v>1.359491964637558</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.72910170592661</v>
+        <v>-10.69667732214475</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.127726962968498</v>
+        <v>-1.114757209455753</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.010390193979656</v>
+        <v>-2.982895913912114</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.3580360273281</v>
+        <v>1.374532595368626</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.46504176760382</v>
+        <v>-10.43261738382195</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.035363303801132</v>
+        <v>-1.022393550288386</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.74633025565686</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.503211674160026</v>
+        <v>1.519708242200551</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.757962144098979</v>
+        <v>-9.725537760317113</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7553184880594981</v>
+        <v>-0.7423487345467517</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.74633025565686</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.500424640499725</v>
+        <v>1.516921208540251</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.717777845732789</v>
+        <v>-9.685353461950923</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7389011448251805</v>
+        <v>-0.7259313913124341</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.706145957290669</v>
+        <v>-2.678651677223127</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.524878843407281</v>
+        <v>1.541375411447807</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.637708050194984</v>
+        <v>-9.605283666413118</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7075064053893017</v>
+        <v>-0.6945366518765557</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.626076161752865</v>
+        <v>-2.598581881685323</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.572287541950721</v>
+        <v>1.588784109991246</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.404226827965385</v>
+        <v>-9.371802444183519</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6061894876596097</v>
+        <v>-0.5932197341468632</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.392594939523267</v>
+        <v>-2.365100659455724</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.720300704126332</v>
+        <v>1.736797272166857</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.224518297821511</v>
+        <v>-9.192093914039646</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5371982859150193</v>
+        <v>-0.5242285324022733</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.335423435360571</v>
+        <v>-2.307929155293028</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.75171139631099</v>
+        <v>1.768207964351516</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.092242824190624</v>
+        <v>-9.059818440408758</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4889206097156373</v>
+        <v>-0.4759508562028913</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.203147961729684</v>
+        <v>-2.175653681662142</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.826444167236549</v>
+        <v>1.842940735277075</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.90164314951747</v>
+        <v>-8.869218765735605</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4098656791587394</v>
+        <v>-0.396895925645993</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.012548287056532</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.943619032728078</v>
+        <v>1.960115600768603</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.652643350833889</v>
+        <v>-8.620218967052024</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2973594184616482</v>
+        <v>-0.2843896649489017</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.012548287056532</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.956525373951736</v>
+        <v>1.973021941992262</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.758233340606994</v>
+        <v>-8.725808956825128</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4675713439701088</v>
+        <v>-0.4546015904573624</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.118138276829636</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.765195450488655</v>
+        <v>1.781692018529181</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.776968242725591</v>
+        <v>-8.744543858943725</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4265209629404612</v>
+        <v>-0.4135512094277147</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.118138276829636</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.813739792365741</v>
+        <v>1.830236360406267</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.629028201317992</v>
+        <v>-8.596603817536126</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.487223869065589</v>
+        <v>-0.4742541155528426</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.097817360921078</v>
+        <v>-2.070323080853536</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.706053419222708</v>
+        <v>1.722549987263234</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.604799564929019</v>
+        <v>-8.572375181147153</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4862464007634779</v>
+        <v>-0.4732766472507319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.073588724532106</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.711876614802613</v>
+        <v>1.728373182843139</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.561251158158328</v>
+        <v>-8.528826774376462</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4757876501502949</v>
+        <v>-0.4628178966375485</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.073588724532106</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.70491600270752</v>
+        <v>1.721412570748046</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.31910276470447</v>
+        <v>-8.286678380922604</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3644659383876085</v>
+        <v>-0.3514961848748621</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.073588724532106</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.719378357088663</v>
+        <v>1.735874925129189</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.255873392936122</v>
+        <v>-8.223449009154256</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3446420692210745</v>
+        <v>-0.3316723157083281</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.073588724532106</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.713910477547858</v>
+        <v>1.730407045588384</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.132582258118992</v>
+        <v>-8.100157874337127</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2978275212836454</v>
+        <v>-0.2848577677708994</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.950297589714976</v>
+        <v>-1.922803309647434</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.785383252448713</v>
+        <v>1.801879820489239</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.11143305921555</v>
+        <v>-8.079008675433684</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2816668634849435</v>
+        <v>-0.2686971099721971</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.929148390811533</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.805773750028105</v>
+        <v>1.82227031806863</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.867667617232105</v>
+        <v>-7.83524323345024</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.188379978344515</v>
+        <v>-0.1754102248317686</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.929148390811533</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.801554458375155</v>
+        <v>1.818051026415681</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.603639550038846</v>
+        <v>-7.57121516625698</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.0806444375471953</v>
+        <v>-0.06767468403444887</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.727282991995579</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.924798011584743</v>
+        <v>1.941294579625269</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.353789156089771</v>
+        <v>-7.321364772307906</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01203779501613678</v>
+        <v>0.02500754852888321</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.727282991995579</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.917540086568446</v>
+        <v>1.934036654608971</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.177897063622339</v>
+        <v>-7.145472679840474</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08599375552375843</v>
+        <v>0.09896350903650486</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.727282991995579</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.921139210089094</v>
+        <v>1.93763577812962</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.006450600599876</v>
+        <v>-6.97402621681801</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1678998467872974</v>
+        <v>0.1808696003000438</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.555836528973116</v>
+        <v>-1.528342248905573</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.037334593957126</v>
+        <v>2.053831161997651</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.781417600931053</v>
+        <v>-6.748993217149187</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2569335242711235</v>
+        <v>0.2699032777838699</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.330803529304293</v>
+        <v>-1.30330924923675</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.171374871374717</v>
+        <v>2.187871439415242</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.566783223294646</v>
+        <v>-6.53435883951278</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3474820763800035</v>
+        <v>0.3604518298927499</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.116169151667886</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.304850299010878</v>
+        <v>2.321346867051404</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.300182866320294</v>
+        <v>-6.267758482538428</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4353164779535401</v>
+        <v>0.4482862314662861</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.116169151667886</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.286044557794674</v>
+        <v>2.302541125835199</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.059752369515434</v>
+        <v>-6.027327985733568</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5332317533003614</v>
+        <v>0.5462015068131079</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8757386548630257</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.432045932502467</v>
+        <v>2.448542500542993</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.816961561865988</v>
+        <v>-5.784537178084123</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6342773901949599</v>
+        <v>0.6472471437077063</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8757386548630257</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.435975246337287</v>
+        <v>2.452471814377813</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.701021712240803</v>
+        <v>-5.668597328458937</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6813319139623739</v>
+        <v>0.6943016674751203</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7989169238469018</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.482746868864302</v>
+        <v>2.499243436904827</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.45836612381764</v>
+        <v>-5.425941740035775</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7753922205516326</v>
+        <v>0.788361974064379</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7989169238469018</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.479744940084295</v>
+        <v>2.496241508124821</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.23834532578063</v>
+        <v>-5.205920941998764</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.864979576777051</v>
+        <v>0.8779493302897974</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6576970787789216</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.566055884135698</v>
+        <v>2.582552452176223</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.039096695875821</v>
+        <v>-5.006672312093955</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9605732115407979</v>
+        <v>0.9735429650535443</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6576970787789216</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.581950066937521</v>
+        <v>2.598446634978046</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.879581592356451</v>
+        <v>-4.847157208574585</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.025525097388848</v>
+        <v>1.038494850901594</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4981819752595517</v>
+        <v>-0.4706876951920093</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.678804973489445</v>
+        <v>2.69530154152997</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.734909447256713</v>
+        <v>-4.702485063474848</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.093482057990183</v>
+        <v>1.106451811502929</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3535098301598142</v>
+        <v>-0.3260155500922718</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.775696363110727</v>
+        <v>2.792192931151253</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.794784274614406</v>
+        <v>-4.76235989083254</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.055569618448531</v>
+        <v>1.068539371961278</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4133846575175064</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.725808958097538</v>
+        <v>2.742305526138063</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.707984776835398</v>
+        <v>-4.675560393053532</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.112689910882701</v>
+        <v>1.125659664395447</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4133846575175064</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.748209451420104</v>
+        <v>2.764706019460629</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.710454483297204</v>
+        <v>-4.678030099515338</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.111774429671391</v>
+        <v>1.124744183184137</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4158543639793125</v>
+        <v>-0.3883600839117701</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.746800028916432</v>
+        <v>2.763296596956958</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.778824669621214</v>
+        <v>-4.746400285839348</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.095433277616489</v>
+        <v>1.108403031129235</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4065786649430976</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.763372370812863</v>
+        <v>2.779868938853388</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.657408239994737</v>
+        <v>-4.624983856212872</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.134436558098971</v>
+        <v>1.147406311611717</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4065786649430976</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.753809079444754</v>
+        <v>2.77030564748528</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.688401399323443</v>
+        <v>-4.592160035905381</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9467488594078752</v>
+        <v>0.9852454047751</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4065786649430976</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.578518644485141</v>
+        <v>2.595015212525666</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.512927139530973</v>
+        <v>-4.416685776112912</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.021505795316651</v>
+        <v>1.060002340683875</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4065786649430976</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.583085876476929</v>
+        <v>2.599582444517454</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.623863392172222</v>
+        <v>-4.527622028754161</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9771427681469489</v>
+        <v>1.015639313514173</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4065786649430976</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.583097350363726</v>
+        <v>2.599593918404252</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.826889969715455</v>
+        <v>-4.730648606297394</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8990635223495611</v>
+        <v>0.9375600677167855</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.609605242486331</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.464412789057692</v>
+        <v>2.480909357098217</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.668964370780162</v>
+        <v>-4.572723007362101</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9724061483558106</v>
+        <v>1.010902693723035</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.609605242486331</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.474585175489824</v>
+        <v>2.49108174353035</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.817285624591291</v>
+        <v>-4.72104426117323</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9080239174052194</v>
+        <v>0.9465204627724439</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.609605242486331</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.469531446063685</v>
+        <v>2.48602801410421</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.818468709242351</v>
+        <v>-4.72222734582429</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8993264589893208</v>
+        <v>0.9378230043565452</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6152482909528425</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.457921392428303</v>
+        <v>2.474417960468829</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.695341002248268</v>
+        <v>-4.599099638830207</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9491294148200555</v>
+        <v>0.9876259601872799</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6152482909528425</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.458473265461405</v>
+        <v>2.47496983350193</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.602530520797409</v>
+        <v>-4.506289157379348</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.915526299291765</v>
+        <v>0.9540228446589896</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5224378095019832</v>
+        <v>-0.4949435294344408</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.443432246223286</v>
+        <v>2.459928814263812</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.553967468576379</v>
+        <v>-4.457726105158318</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9368249961047779</v>
+        <v>0.9753215414720022</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.473874757280953</v>
+        <v>-0.4463804772134106</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.474443553480505</v>
+        <v>2.490940121521031</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.441296250340129</v>
+        <v>-4.345054886922068</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9769691919110008</v>
+        <v>1.015465737278225</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3612035390447028</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.537121992933978</v>
+        <v>2.553618560974503</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.328919249157456</v>
+        <v>-4.232677885739395</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.027411288214737</v>
+        <v>1.065907833581962</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3612035390447028</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.542613288764645</v>
+        <v>2.559109856805171</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.527153818044186</v>
+        <v>-4.430912454626125</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9596146624285842</v>
+        <v>0.9981112077958085</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5594381079314333</v>
+        <v>-0.5319438278638909</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.435169749201146</v>
+        <v>2.451666317241671</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.610155099069465</v>
+        <v>-4.513913735651404</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7647698700191259</v>
+        <v>0.8032664153863502</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5780089924586072</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.262382938485495</v>
+        <v>2.278879506526021</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.450960827012889</v>
+        <v>-4.354719463594828</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9485972395609621</v>
+        <v>0.9870937849281864</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5780089924586072</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.382532599204701</v>
+        <v>2.399029167245226</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.537559409993992</v>
+        <v>-4.441318046575931</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9284708324708439</v>
+        <v>0.9669673778380683</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5780089924586072</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.397045625307024</v>
+        <v>2.413542193347549</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.745014477547768</v>
+        <v>3.748951885876318</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.49917574743584</v>
+        <v>-4.402934384017779</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9412437388364729</v>
+        <v>0.9797402842036975</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.539625329900456</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.417495264184283</v>
+        <v>2.433991832224809</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-37.5%</t>
+          <t>-8.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>115.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>135.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-693.6%</t>
+          <t>-696.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-57.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.9%</t>
+          <t>-604.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-279.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-41.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.1%</t>
+          <t>-92.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.2%</t>
+          <t>-258.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-317.8%</t>
+          <t>-320.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-36.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-155.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.2%</t>
+          <t>-277.9%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-191.1%</t>
+          <t>-192.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-31.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-202.6%</t>
+          <t>-143.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1954"/>
+  <dimension ref="A1:G1955"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.319973263478165</v>
+        <v>-5.348897333008768</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9840105793278613</v>
+        <v>0.9724409515156198</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9380883224177073</v>
+        <v>-0.9646795056947095</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.549503315582251</v>
+        <v>2.533548605616049</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.655635910708617</v>
+        <v>-5.684559980239221</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8483261120916454</v>
+        <v>0.836756484279404</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9380883224177073</v>
+        <v>-0.9646795056947095</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.548083907238215</v>
+        <v>2.532129197272014</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.019262155608931</v>
+        <v>-6.048186225139534</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7093631743657616</v>
+        <v>0.6977935465535201</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.036309959284833</v>
+        <v>-1.062901142561835</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.495638485352182</v>
+        <v>2.47968377538598</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.384389538247677</v>
+        <v>-6.413313607778281</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5625667363160942</v>
+        <v>0.5509971085038532</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.332620743583846</v>
+        <v>-1.359211926860848</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.317106529778606</v>
+        <v>2.301151819812404</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.792978315428355</v>
+        <v>-6.821902384958959</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3978927694585823</v>
+        <v>0.3863231416463409</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.767800704041526</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.070714807484958</v>
+        <v>2.054760097518757</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.205960799569449</v>
+        <v>-7.234884869100052</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2278852082736051</v>
+        <v>0.2163155804613641</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.767800704041526</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.065900239956418</v>
+        <v>2.049945529990217</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.622352673856446</v>
+        <v>-7.65127674338705</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.05932250916768389</v>
+        <v>0.04775288135544242</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.767800704041526</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063894290565296</v>
+        <v>2.047939580599095</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-8.027953753916893</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.09265923218781591</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.767800704041526</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.074152981233975</v>
+        <v>2.058198271267774</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.373828575901703</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.2349095958360445</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.767800704041526</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.070252546379669</v>
+        <v>2.054297836413468</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.535970846364796</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.3013615839662811</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741209520764524</v>
+        <v>-1.767800704041526</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.06865746643467</v>
+        <v>2.052702756468469</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.832632188174994</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.4162471447611522</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.836543839775405</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.031190560923552</v>
+        <v>2.01523585095735</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.265981296285229</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5936130925396492</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.836543839775405</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.027164256389149</v>
+        <v>2.011209546422947</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.64898268502786</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.7469157493582856</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.809952656498403</v>
+        <v>-1.836543839775405</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.027062155067564</v>
+        <v>2.011107445101363</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.806381565240981</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.8073037854721039</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.993942719988526</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>1.919239632944921</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.16591188774498</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.9457656111756547</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.993942719988526</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>1.924589936242971</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.49231191641</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.068409602684482</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.320342748653539</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.736665939001141</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.71146088448419</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.153027439292392</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.539491716727736</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.608218308778391</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.70776995952778</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.151551069309828</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.539491716727736</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.608218308778391</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.91202813485765</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.227741142323131</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.667130661341725</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.53714813912864</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-11.13006590648882</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.310473696491166</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.841901429437624</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.436768232755537</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-11.05659607482137</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.265714062330765</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.768431597770176</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.496221833249427</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.23172049220792</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.321208608537866</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.943556015156719</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.405702403565017</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.46617258622241</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.422208611045258</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.943556015156719</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.398483238663421</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.75397643075965</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.544002339634129</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.231359859693958</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.219128741167102</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.98380087792347</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.634816328661103</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.394007396764118</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.122656008763562</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.21582979765973</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.724934167926493</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.456020093952541</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.088142119079623</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.16381428369092</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.700137626652567</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.456020093952541</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.092132454766024</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.30548612541504</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.758281590240957</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.456020093952541</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.090657227867282</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.25589528099021</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.723391842306151</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.406429249527708</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.135465144687055</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-12.05674317375311</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.656782133057994</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.241106723577894</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.22160752661026</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.8308980210337</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.556864998934021</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.199180047990731</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.256342604998767</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.70631936469611</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.505894391842926</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.199180047990731</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.257481749554826</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.75921465274039</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.524418732898533</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.194224701902284</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.263088731370001</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.47530592181164</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.405121536288397</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.194224701902284</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.268822435608637</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.403939529202</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.386312241638403</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.122858309292636</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.317859718746762</v>
+        <v>1.301905008780561</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-11.14010266199793</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.290660976069682</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.122858309292636</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.307976237433855</v>
+        <v>1.292021527467653</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84393679159892</v>
+        <v>-10.87286086112953</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174029188409456</v>
+        <v>-1.185598816221697</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.122858309292636</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.306141676934481</v>
+        <v>1.29018696696828</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.72063086312071</v>
+        <v>-10.74955493265131</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.125007131991629</v>
+        <v>-1.136576759803871</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.006849454888072</v>
+        <v>-3.033440638165074</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.359491964637558</v>
+        <v>1.343537254671356</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.69667732214475</v>
+        <v>-10.72560139167535</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.114757209455753</v>
+        <v>-1.126326837267994</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.982895913912114</v>
+        <v>-3.009487097189116</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.374532595368626</v>
+        <v>1.358577885402424</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.43261738382195</v>
+        <v>-10.46154145335255</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.022393550288386</v>
+        <v>-1.033963178100628</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.74542715886632</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.519708242200551</v>
+        <v>1.50375353223435</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.725537760317113</v>
+        <v>-9.754461829847717</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7423487345467517</v>
+        <v>-0.7539183623589931</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.718835975589318</v>
+        <v>-2.74542715886632</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.516921208540251</v>
+        <v>1.500966498574049</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.685353461950923</v>
+        <v>-9.714277531481526</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7259313913124341</v>
+        <v>-0.7375010191246756</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.678651677223127</v>
+        <v>-2.705242860500129</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.541375411447807</v>
+        <v>1.525420701481605</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.605283666413118</v>
+        <v>-9.634207735943722</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6945366518765557</v>
+        <v>-0.7061062796887967</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.598581881685323</v>
+        <v>-2.625173064962325</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.588784109991246</v>
+        <v>1.572829400025044</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.371802444183519</v>
+        <v>-9.400726513714122</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5932197341468632</v>
+        <v>-0.6047893619591047</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.365100659455724</v>
+        <v>-2.391691842732727</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.736797272166857</v>
+        <v>1.720842562200656</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.192093914039646</v>
+        <v>-9.221017983570249</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5242285324022733</v>
+        <v>-0.5357981602145143</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.307929155293028</v>
+        <v>-2.334520338570031</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.768207964351516</v>
+        <v>1.752253254385314</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.059818440408758</v>
+        <v>-9.088742509939362</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4759508562028913</v>
+        <v>-0.4875204840151324</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.175653681662142</v>
+        <v>-2.202244864939144</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.842940735277075</v>
+        <v>1.826986025310873</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.869218765735605</v>
+        <v>-8.898142835266208</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.396895925645993</v>
+        <v>-0.4084655534582344</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.985054006988989</v>
+        <v>-2.011645190265992</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.960115600768603</v>
+        <v>1.944160890802402</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.620218967052024</v>
+        <v>-8.649143036582627</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2843896649489017</v>
+        <v>-0.2959592927611432</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.985054006988989</v>
+        <v>-2.011645190265992</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.973021941992262</v>
+        <v>1.95706723202606</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.725808956825128</v>
+        <v>-8.754733026355732</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4546015904573624</v>
+        <v>-0.4661712182696038</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.117235180039096</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.781692018529181</v>
+        <v>1.765737308562979</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.744543858943725</v>
+        <v>-8.773467928474329</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4135512094277147</v>
+        <v>-0.4251208372399562</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.090643996762093</v>
+        <v>-2.117235180039096</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.830236360406267</v>
+        <v>1.814281650440065</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.596603817536126</v>
+        <v>-8.625527887066729</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4742541155528426</v>
+        <v>-0.485823743365084</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.070323080853536</v>
+        <v>-2.096914264130538</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.722549987263234</v>
+        <v>1.706595277297032</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.572375181147153</v>
+        <v>-8.601299250677757</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4732766472507319</v>
+        <v>-0.4848462750629734</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.072685627741566</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.728373182843139</v>
+        <v>1.712418472876937</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.528826774376462</v>
+        <v>-8.557750843907066</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4628178966375485</v>
+        <v>-0.4743875244497899</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.072685627741566</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.721412570748046</v>
+        <v>1.705457860781844</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.286678380922604</v>
+        <v>-8.315602450453207</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3514961848748621</v>
+        <v>-0.3630658126871036</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.072685627741566</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.735874925129189</v>
+        <v>1.719920215162987</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.223449009154256</v>
+        <v>-8.25237307868486</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3316723157083281</v>
+        <v>-0.3432419435205696</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.046094444464564</v>
+        <v>-2.072685627741566</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.730407045588384</v>
+        <v>1.714452335622182</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.100157874337127</v>
+        <v>-8.12908194386773</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2848577677708994</v>
+        <v>-0.2964273955831405</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.922803309647434</v>
+        <v>-1.949394492924436</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.801879820489239</v>
+        <v>1.785925110523038</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.079008675433684</v>
+        <v>-8.107932744964288</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2686971099721971</v>
+        <v>-0.2802667377844386</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.928245294020992</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.82227031806863</v>
+        <v>1.806315608102429</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.83524323345024</v>
+        <v>-7.864167302980843</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1754102248317686</v>
+        <v>-0.1869798526440101</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.90165411074399</v>
+        <v>-1.928245294020992</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.818051026415681</v>
+        <v>1.802096316449479</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.57121516625698</v>
+        <v>-7.600139235787584</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.06767468403444887</v>
+        <v>-0.07924431184669034</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.726379895205039</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.941294579625269</v>
+        <v>1.925339869659068</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.321364772307906</v>
+        <v>-7.350288841838509</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.02500754852888321</v>
+        <v>0.01343792071664174</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.726379895205039</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.934036654608971</v>
+        <v>1.91808194464277</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.145472679840474</v>
+        <v>-7.174396749371077</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.09896350903650486</v>
+        <v>0.08739388122426339</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.699788711928037</v>
+        <v>-1.726379895205039</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.93763577812962</v>
+        <v>1.921681068163418</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.97402621681801</v>
+        <v>-7.002950286348613</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1808696003000438</v>
+        <v>0.1692999724878024</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528342248905573</v>
+        <v>-1.554933432182576</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.053831161997651</v>
+        <v>2.03787645203145</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.748993217149187</v>
+        <v>-6.777917286679791</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2699032777838699</v>
+        <v>0.2583336499716284</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.30330924923675</v>
+        <v>-1.329900432513753</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.187871439415242</v>
+        <v>2.171916729449041</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353075</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.53435883951278</v>
+        <v>-6.563282909043384</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3604518298927499</v>
+        <v>0.3488822020805085</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.115266054877346</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.321346867051404</v>
+        <v>2.305392157085202</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544784</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.267758482538428</v>
+        <v>-6.296682552069032</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4482862314662861</v>
+        <v>0.4367166036540451</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.088674871600344</v>
+        <v>-1.115266054877346</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.302541125835199</v>
+        <v>2.286586415868998</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.027327985733568</v>
+        <v>-6.056252055264172</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5462015068131079</v>
+        <v>0.5346318790008664</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.8748355580724856</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.448542500542993</v>
+        <v>2.432587790576791</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.784537178084123</v>
+        <v>-5.813461247614726</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6472471437077063</v>
+        <v>0.6356775158954648</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8482443747954833</v>
+        <v>-0.8748355580724856</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.452471814377813</v>
+        <v>2.436517104411612</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.668597328458937</v>
+        <v>-5.697521397989541</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6943016674751203</v>
+        <v>0.6827320396628789</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.7980138270563617</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.499243436904827</v>
+        <v>2.483288726938626</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.425941740035775</v>
+        <v>-5.454865809566378</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.788361974064379</v>
+        <v>0.7767923462521376</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7714226437793594</v>
+        <v>-0.7980138270563617</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.496241508124821</v>
+        <v>2.48028679815862</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.205920941998764</v>
+        <v>-5.234845011529368</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8779493302897974</v>
+        <v>0.8663797024775559</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.6567939819883815</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.582552452176223</v>
+        <v>2.566597742210022</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.006672312093955</v>
+        <v>-5.035596381624559</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9735429650535443</v>
+        <v>0.9619733372413029</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6302027987113792</v>
+        <v>-0.6567939819883815</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.598446634978046</v>
+        <v>2.582491925011845</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.847157208574585</v>
+        <v>-4.876081278105189</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.038494850901594</v>
+        <v>1.026925223089353</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4706876951920093</v>
+        <v>-0.4972788784690115</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.69530154152997</v>
+        <v>2.679346831563769</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.702485063474848</v>
+        <v>-4.731409133005451</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.106451811502929</v>
+        <v>1.094882183690687</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3260155500922718</v>
+        <v>-0.3526067333692741</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.792192931151253</v>
+        <v>2.776238221185051</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.76235989083254</v>
+        <v>-4.791283960363144</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.068539371961278</v>
+        <v>1.056969744149036</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.4124815607269662</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.742305526138063</v>
+        <v>2.726350816171862</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.675560393053532</v>
+        <v>-4.704484462584135</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.125659664395447</v>
+        <v>1.114090036583206</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.385890377449964</v>
+        <v>-0.4124815607269662</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.764706019460629</v>
+        <v>2.748751309494428</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.678030099515338</v>
+        <v>-4.706954169045941</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.124744183184137</v>
+        <v>1.113174555371895</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3883600839117701</v>
+        <v>-0.4149512671887724</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.763296596956958</v>
+        <v>2.747341886990756</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.746400285839348</v>
+        <v>-4.775324355369952</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.108403031129235</v>
+        <v>1.096833403316994</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4056755681525575</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.779868938853388</v>
+        <v>2.763914228887187</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.624983856212872</v>
+        <v>-4.653907925743475</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.147406311611717</v>
+        <v>1.135836683799475</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4056755681525575</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.77030564748528</v>
+        <v>2.754350937519078</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>3.031299837586259</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.592160035905381</v>
+        <v>-4.620066073187471</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9852454047751</v>
+        <v>1.182916983997523</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4056755681525575</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.595015212525666</v>
+        <v>2.787894496694725</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>3.035867069578047</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.416685776112912</v>
+        <v>-4.444591813395002</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.060002340683875</v>
+        <v>1.257673919906299</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4056755681525575</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.599582444517454</v>
+        <v>2.792461728686512</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.827044549329585</v>
+        <v>3.035878543464844</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.527622028754161</v>
+        <v>-4.555528066036251</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.015639313514173</v>
+        <v>1.213310892736597</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3790843848755552</v>
+        <v>-0.4056755681525575</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.599593918404252</v>
+        <v>2.79247320257331</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.83017593454949</v>
+        <v>3.03900992868475</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.730648606297394</v>
+        <v>-4.758554643579484</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9375600677167855</v>
+        <v>1.135231646939209</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.6087021456957908</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.480909357098217</v>
+        <v>2.673788641267275</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.840348320981623</v>
+        <v>3.049182315116882</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.572723007362101</v>
+        <v>-4.600629044644191</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.010902693723035</v>
+        <v>1.208574272945458</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.6087021456957908</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.49108174353035</v>
+        <v>2.683961027699408</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.835294591555483</v>
+        <v>3.044128585690742</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.72104426117323</v>
+        <v>-4.74895029845532</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9465204627724439</v>
+        <v>1.144192041994867</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5821109624187886</v>
+        <v>-0.6087021456957908</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.48602801410421</v>
+        <v>2.678907298273268</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.827070367000009</v>
+        <v>3.035904361135268</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.72222734582429</v>
+        <v>-4.75013338310638</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9378230043565452</v>
+        <v>1.135494583578968</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.6143451941623024</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.474417960468829</v>
+        <v>2.667297244637887</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.82762224003311</v>
+        <v>3.036456234168369</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.599099638830207</v>
+        <v>-4.627005676112297</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9876259601872799</v>
+        <v>1.185297539409703</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5877540108853001</v>
+        <v>-0.6143451941623024</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.47496983350193</v>
+        <v>2.667849117670988</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.756894931924476</v>
+        <v>2.965728926059735</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.506289157379348</v>
+        <v>-4.534195194661438</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9540228446589896</v>
+        <v>1.151694423881413</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4949435294344408</v>
+        <v>-0.521534712711443</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.459928814263812</v>
+        <v>2.65280809843287</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.758768407849077</v>
+        <v>2.967602401984336</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.457726105158318</v>
+        <v>-4.485632142440408</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9753215414720022</v>
+        <v>1.172993120694426</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4463804772134106</v>
+        <v>-0.4729716604904128</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.490940121521031</v>
+        <v>2.683819405690088</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.7538441163608</v>
+        <v>2.962678110496059</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.345054886922068</v>
+        <v>-4.372960924204158</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.015465737278225</v>
+        <v>1.213137316500648</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.3603004422541626</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.553618560974503</v>
+        <v>2.746497845143562</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.759335412191467</v>
+        <v>2.968169406326726</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.232677885739395</v>
+        <v>-4.260583923021485</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.065907833581962</v>
+        <v>1.263579412804385</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3337092589771604</v>
+        <v>-0.3603004422541626</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.559109856805171</v>
+        <v>2.751989140974229</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.770832613960006</v>
+        <v>2.979666608095265</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.430912454626125</v>
+        <v>-4.458818491908215</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9981112077958085</v>
+        <v>1.195782787018232</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5319438278638909</v>
+        <v>-0.5585350111408932</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.451666317241671</v>
+        <v>2.64454560141073</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.609188333960659</v>
+        <v>2.818022328095918</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.513913735651404</v>
+        <v>-4.541819772933494</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8032664153863502</v>
+        <v>1.000937994608774</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.577105895668067</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.278879506526021</v>
+        <v>2.471758790695079</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.729337994679865</v>
+        <v>2.938171988815124</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.354719463594828</v>
+        <v>-4.382625500876918</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9870937849281864</v>
+        <v>1.18476536415061</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.577105895668067</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.399029167245226</v>
+        <v>2.591908451414284</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.743851020782188</v>
+        <v>2.952685014917447</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.441318046575931</v>
+        <v>-4.469224083858021</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9669673778380683</v>
+        <v>1.164638957060492</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5505147123910648</v>
+        <v>-0.577105895668067</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.413542193347549</v>
+        <v>2.606421477516607</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,45 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.748951885876318</v>
+        <v>3.741170494383429</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.741270462124556</v>
+        <v>2.950104456259816</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.402934384017779</v>
+        <v>-4.43084042129987</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9797402842036975</v>
+        <v>1.177411863426121</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.5387222331099158</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.433991832224809</v>
+        <v>2.626871116393867</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="2" t="n">
+        <v>45417</v>
+      </c>
+      <c r="B1955" t="n">
+        <v>3.748888891187271</v>
+      </c>
+      <c r="C1955" t="n">
+        <v>3.031417980059448</v>
+      </c>
+      <c r="D1955" t="n">
+        <v>-4.43084042129987</v>
+      </c>
+      <c r="E1955" t="n">
+        <v>1.177411863426121</v>
+      </c>
+      <c r="F1955" t="n">
+        <v>-0.5387222331099158</v>
+      </c>
+      <c r="G1955" t="n">
+        <v>3.024481777045816</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.5%</t>
+          <t>115.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.7%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-696.5%</t>
+          <t>-693.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.1%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.7%</t>
+          <t>-601.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-279.0%</t>
+          <t>-277.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.6%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-92.7%</t>
+          <t>-84.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-258.5%</t>
+          <t>-278.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-320.5%</t>
+          <t>-317.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-36.4%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.9%</t>
+          <t>-275.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-192.7%</t>
+          <t>-191.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.4%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-143.6%</t>
+          <t>-164.5%</t>
         </is>
       </c>
     </row>
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.348897333008768</v>
+        <v>-5.319973263478165</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9724409515156198</v>
+        <v>0.9840105793278613</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9646795056947095</v>
+        <v>-0.9380883224177073</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.533548605616049</v>
+        <v>2.549503315582251</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.684559980239221</v>
+        <v>-5.655635910708617</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.836756484279404</v>
+        <v>0.8483261120916454</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9646795056947095</v>
+        <v>-0.9380883224177073</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.532129197272014</v>
+        <v>2.548083907238215</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.048186225139534</v>
+        <v>-6.019262155608931</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6977935465535201</v>
+        <v>0.7093631743657616</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.062901142561835</v>
+        <v>-1.036309959284833</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.47968377538598</v>
+        <v>2.495638485352182</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.413313607778281</v>
+        <v>-6.384389538247677</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5509971085038532</v>
+        <v>0.5625667363160942</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.359211926860848</v>
+        <v>-1.332620743583846</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.301151819812404</v>
+        <v>2.317106529778606</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.821902384958959</v>
+        <v>-6.792978315428355</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3863231416463409</v>
+        <v>0.3978927694585823</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.767800704041526</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.054760097518757</v>
+        <v>2.070714807484958</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.234884869100052</v>
+        <v>-7.205960799569449</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2163155804613641</v>
+        <v>0.2278852082736051</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.767800704041526</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.049945529990217</v>
+        <v>2.065900239956418</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.65127674338705</v>
+        <v>-7.622352673856446</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.04775288135544242</v>
+        <v>0.05932250916768389</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.767800704041526</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.047939580599095</v>
+        <v>2.063894290565296</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.027953753916893</v>
+        <v>-7.999029684386291</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.09265923218781591</v>
+        <v>-0.08108960437557489</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.767800704041526</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.058198271267774</v>
+        <v>2.074152981233975</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.373828575901703</v>
+        <v>-8.344904506371099</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2349095958360445</v>
+        <v>-0.2233399680238031</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.767800704041526</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.054297836413468</v>
+        <v>2.070252546379669</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.535970846364796</v>
+        <v>-8.507046776834192</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3013615839662811</v>
+        <v>-0.2897919561540396</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.767800704041526</v>
+        <v>-1.741209520764524</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.052702756468469</v>
+        <v>2.06865746643467</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.832632188174994</v>
+        <v>-8.803708118644391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4162471447611522</v>
+        <v>-0.4046775169489107</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.836543839775405</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.01523585095735</v>
+        <v>2.031190560923552</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.265981296285229</v>
+        <v>-9.237057226754626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5936130925396492</v>
+        <v>-0.5820434647274078</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.836543839775405</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.011209546422947</v>
+        <v>2.027164256389149</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.64898268502786</v>
+        <v>-9.620058615497257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7469157493582856</v>
+        <v>-0.7353461215460442</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.836543839775405</v>
+        <v>-1.809952656498403</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.011107445101363</v>
+        <v>2.027062155067564</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.806381565240981</v>
+        <v>-9.777457495710378</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8073037854721039</v>
+        <v>-0.7957341576598624</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.993942719988526</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.919239632944921</v>
+        <v>1.935194342911122</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.16591188774498</v>
+        <v>-10.13698781821438</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9457656111756547</v>
+        <v>-0.9341959833634128</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.993942719988526</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.924589936242971</v>
+        <v>1.940544646209172</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.49231191641</v>
+        <v>-10.46338784687939</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.068409602684482</v>
+        <v>-1.05683997487224</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.320342748653539</v>
+        <v>-2.293751565376537</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.736665939001141</v>
+        <v>1.752620648967342</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.71146088448419</v>
+        <v>-10.68253681495359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.153027439292392</v>
+        <v>-1.141457811480151</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.539491716727736</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.608218308778391</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.70776995952778</v>
+        <v>-10.67884588999718</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.151551069309828</v>
+        <v>-1.139981441497586</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.539491716727736</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.608218308778391</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.91202813485765</v>
+        <v>-10.88310406532704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.227741142323131</v>
+        <v>-1.21617151451089</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.667130661341725</v>
+        <v>-2.640539478064723</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.53714813912864</v>
+        <v>1.553102849094841</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.13006590648882</v>
+        <v>-11.10114183695822</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.310473696491166</v>
+        <v>-1.298904068678925</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.841901429437624</v>
+        <v>-2.815310246160622</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.436768232755537</v>
+        <v>1.452722942721738</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.05659607482137</v>
+        <v>-11.02767200529077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.265714062330765</v>
+        <v>-1.254144434518524</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.768431597770176</v>
+        <v>-2.741840414493173</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.496221833249427</v>
+        <v>1.512176543215628</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.23172049220792</v>
+        <v>-11.20279642267731</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.321208608537866</v>
+        <v>-1.309638980725625</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.943556015156719</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.405702403565017</v>
+        <v>1.421657113531219</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.46617258622241</v>
+        <v>-11.4372485166918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.422208611045258</v>
+        <v>-1.410638983233016</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.943556015156719</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.398483238663421</v>
+        <v>1.414437948629623</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.75397643075965</v>
+        <v>-11.72505236122904</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.544002339634129</v>
+        <v>-1.532432711821888</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.231359859693958</v>
+        <v>-3.204768676416955</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.219128741167102</v>
+        <v>1.235083451133304</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.98380087792347</v>
+        <v>-11.95487680839287</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.634816328661103</v>
+        <v>-1.623246700848862</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.394007396764118</v>
+        <v>-3.367416213487116</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.122656008763562</v>
+        <v>1.138610718729764</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.21582979765973</v>
+        <v>-12.18690572812913</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.724934167926493</v>
+        <v>-1.713364540114252</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.456020093952541</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.088142119079623</v>
+        <v>1.104096829045825</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.16381428369092</v>
+        <v>-12.13489021416032</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.700137626652567</v>
+        <v>-1.688567998840326</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.456020093952541</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.092132454766024</v>
+        <v>1.108087164732225</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.30548612541504</v>
+        <v>-12.27656205588444</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.758281590240957</v>
+        <v>-1.746711962428716</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.456020093952541</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.090657227867282</v>
+        <v>1.106611937833484</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.25589528099021</v>
+        <v>-12.2269712114596</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.723391842306151</v>
+        <v>-1.71182221449391</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.406429249527708</v>
+        <v>-3.379838066250705</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.135465144687055</v>
+        <v>1.151419854653256</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.05674317375311</v>
+        <v>-12.0278191042225</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.656782133057994</v>
+        <v>-1.645212505245753</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.241106723577894</v>
+        <v>-3.214515540300892</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.22160752661026</v>
+        <v>1.237562236576461</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.8308980210337</v>
+        <v>-11.80197395150309</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.556864998934021</v>
+        <v>-1.54529537112178</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.199180047990731</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.256342604998767</v>
+        <v>1.272297314964968</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.70631936469611</v>
+        <v>-11.6773952951655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.505894391842926</v>
+        <v>-1.494324764030684</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.199180047990731</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.257481749554826</v>
+        <v>1.273436459521027</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.75921465274039</v>
+        <v>-11.73029058320979</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.524418732898533</v>
+        <v>-1.512849105086292</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.194224701902284</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.263088731370001</v>
+        <v>1.279043441336202</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.47530592181164</v>
+        <v>-11.44638185228104</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.405121536288397</v>
+        <v>-1.393551908476155</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.194224701902284</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.268822435608637</v>
+        <v>1.284777145574839</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.403939529202</v>
+        <v>-11.37501545967139</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.386312241638403</v>
+        <v>-1.374742613826162</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.122858309292636</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.301905008780561</v>
+        <v>1.317859718746762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14010266199793</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.290660976069682</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.122858309292636</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.292021527467653</v>
+        <v>1.307976237433855</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87286086112953</v>
+        <v>-10.84393679159892</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.185598816221697</v>
+        <v>-1.174029188409456</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.122858309292636</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.29018696696828</v>
+        <v>1.306141676934481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74955493265131</v>
+        <v>-10.72063086312071</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.136576759803871</v>
+        <v>-1.125007131991629</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.033440638165074</v>
+        <v>-3.006849454888072</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.343537254671356</v>
+        <v>1.359491964637558</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.72560139167535</v>
+        <v>-10.69667732214475</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.126326837267994</v>
+        <v>-1.114757209455753</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.009487097189116</v>
+        <v>-2.982895913912114</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.358577885402424</v>
+        <v>1.374532595368626</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.46154145335255</v>
+        <v>-10.43261738382195</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.033963178100628</v>
+        <v>-1.022393550288386</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.74542715886632</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.50375353223435</v>
+        <v>1.519708242200551</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.754461829847717</v>
+        <v>-9.725537760317113</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7539183623589931</v>
+        <v>-0.7423487345467517</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.74542715886632</v>
+        <v>-2.718835975589318</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.500966498574049</v>
+        <v>1.516921208540251</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.714277531481526</v>
+        <v>-9.685353461950923</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7375010191246756</v>
+        <v>-0.7259313913124341</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.705242860500129</v>
+        <v>-2.678651677223127</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.525420701481605</v>
+        <v>1.541375411447807</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.634207735943722</v>
+        <v>-9.605283666413118</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7061062796887967</v>
+        <v>-0.6945366518765557</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.625173064962325</v>
+        <v>-2.598581881685323</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.572829400025044</v>
+        <v>1.588784109991246</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.400726513714122</v>
+        <v>-9.371802444183519</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6047893619591047</v>
+        <v>-0.5932197341468632</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.391691842732727</v>
+        <v>-2.365100659455724</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.720842562200656</v>
+        <v>1.736797272166857</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.221017983570249</v>
+        <v>-9.192093914039646</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5357981602145143</v>
+        <v>-0.5242285324022733</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.334520338570031</v>
+        <v>-2.307929155293028</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.752253254385314</v>
+        <v>1.768207964351516</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.088742509939362</v>
+        <v>-9.059818440408758</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4875204840151324</v>
+        <v>-0.4759508562028913</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.202244864939144</v>
+        <v>-2.175653681662142</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.826986025310873</v>
+        <v>1.842940735277075</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.898142835266208</v>
+        <v>-8.869218765735605</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4084655534582344</v>
+        <v>-0.396895925645993</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.011645190265992</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.944160890802402</v>
+        <v>1.960115600768603</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.649143036582627</v>
+        <v>-8.620218967052024</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2959592927611432</v>
+        <v>-0.2843896649489017</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.011645190265992</v>
+        <v>-1.985054006988989</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.95706723202606</v>
+        <v>1.973021941992262</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.754733026355732</v>
+        <v>-8.725808956825128</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4661712182696038</v>
+        <v>-0.4546015904573624</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.117235180039096</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.765737308562979</v>
+        <v>1.781692018529181</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.773467928474329</v>
+        <v>-8.744543858943725</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4251208372399562</v>
+        <v>-0.4135512094277147</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.117235180039096</v>
+        <v>-2.090643996762093</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.814281650440065</v>
+        <v>1.830236360406267</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.625527887066729</v>
+        <v>-8.596603817536126</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.485823743365084</v>
+        <v>-0.4742541155528426</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.096914264130538</v>
+        <v>-2.070323080853536</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.706595277297032</v>
+        <v>1.722549987263234</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.601299250677757</v>
+        <v>-8.572375181147153</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4848462750629734</v>
+        <v>-0.4732766472507319</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.072685627741566</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.712418472876937</v>
+        <v>1.728373182843139</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.557750843907066</v>
+        <v>-8.528826774376462</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4743875244497899</v>
+        <v>-0.4628178966375485</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.072685627741566</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.705457860781844</v>
+        <v>1.721412570748046</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.315602450453207</v>
+        <v>-8.286678380922604</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3630658126871036</v>
+        <v>-0.3514961848748621</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.072685627741566</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.719920215162987</v>
+        <v>1.735874925129189</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.25237307868486</v>
+        <v>-8.223449009154256</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3432419435205696</v>
+        <v>-0.3316723157083281</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.072685627741566</v>
+        <v>-2.046094444464564</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.714452335622182</v>
+        <v>1.730407045588384</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.12908194386773</v>
+        <v>-8.100157874337127</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2964273955831405</v>
+        <v>-0.2848577677708994</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.949394492924436</v>
+        <v>-1.922803309647434</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.785925110523038</v>
+        <v>1.801879820489239</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.107932744964288</v>
+        <v>-8.079008675433684</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2802667377844386</v>
+        <v>-0.2686971099721971</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.928245294020992</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.806315608102429</v>
+        <v>1.82227031806863</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.864167302980843</v>
+        <v>-7.83524323345024</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1869798526440101</v>
+        <v>-0.1754102248317686</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.928245294020992</v>
+        <v>-1.90165411074399</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.802096316449479</v>
+        <v>1.818051026415681</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.600139235787584</v>
+        <v>-7.57121516625698</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07924431184669034</v>
+        <v>-0.06767468403444887</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.726379895205039</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.925339869659068</v>
+        <v>1.941294579625269</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.350288841838509</v>
+        <v>-7.321364772307906</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01343792071664174</v>
+        <v>0.02500754852888321</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.726379895205039</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.91808194464277</v>
+        <v>1.934036654608971</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.174396749371077</v>
+        <v>-7.145472679840474</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08739388122426339</v>
+        <v>0.09896350903650486</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.726379895205039</v>
+        <v>-1.699788711928037</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.921681068163418</v>
+        <v>1.93763577812962</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.002950286348613</v>
+        <v>-6.97402621681801</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1692999724878024</v>
+        <v>0.1808696003000438</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.554933432182576</v>
+        <v>-1.528342248905573</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.03787645203145</v>
+        <v>2.053831161997651</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.777917286679791</v>
+        <v>-6.748993217149187</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2583336499716284</v>
+        <v>0.2699032777838699</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.329900432513753</v>
+        <v>-1.30330924923675</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.171916729449041</v>
+        <v>2.187871439415242</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.563282909043384</v>
+        <v>-6.53435883951278</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3488822020805085</v>
+        <v>0.3604518298927499</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.115266054877346</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.305392157085202</v>
+        <v>2.321346867051404</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.296682552069032</v>
+        <v>-6.267758482538428</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4367166036540451</v>
+        <v>0.4482862314662861</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.115266054877346</v>
+        <v>-1.088674871600344</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.286586415868998</v>
+        <v>2.302541125835199</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.056252055264172</v>
+        <v>-6.027327985733568</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5346318790008664</v>
+        <v>0.5462015068131079</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8748355580724856</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.432587790576791</v>
+        <v>2.448542500542993</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.813461247614726</v>
+        <v>-5.784537178084123</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6356775158954648</v>
+        <v>0.6472471437077063</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8748355580724856</v>
+        <v>-0.8482443747954833</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.436517104411612</v>
+        <v>2.452471814377813</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.697521397989541</v>
+        <v>-5.668597328458937</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6827320396628789</v>
+        <v>0.6943016674751203</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7980138270563617</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.483288726938626</v>
+        <v>2.499243436904827</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.454865809566378</v>
+        <v>-5.425941740035775</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7767923462521376</v>
+        <v>0.788361974064379</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7980138270563617</v>
+        <v>-0.7714226437793594</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.48028679815862</v>
+        <v>2.496241508124821</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.234845011529368</v>
+        <v>-5.205920941998764</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8663797024775559</v>
+        <v>0.8779493302897974</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6567939819883815</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.566597742210022</v>
+        <v>2.582552452176223</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.035596381624559</v>
+        <v>-5.006672312093955</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9619733372413029</v>
+        <v>0.9735429650535443</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6567939819883815</v>
+        <v>-0.6302027987113792</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.582491925011845</v>
+        <v>2.598446634978046</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.876081278105189</v>
+        <v>-4.847157208574585</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.026925223089353</v>
+        <v>1.038494850901594</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4972788784690115</v>
+        <v>-0.4706876951920093</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.679346831563769</v>
+        <v>2.69530154152997</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.731409133005451</v>
+        <v>-4.702485063474848</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.094882183690687</v>
+        <v>1.106451811502929</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3526067333692741</v>
+        <v>-0.3260155500922718</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.776238221185051</v>
+        <v>2.792192931151253</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.791283960363144</v>
+        <v>-4.76235989083254</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.056969744149036</v>
+        <v>1.068539371961278</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4124815607269662</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.726350816171862</v>
+        <v>2.742305526138063</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.704484462584135</v>
+        <v>-4.675560393053532</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.114090036583206</v>
+        <v>1.125659664395447</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4124815607269662</v>
+        <v>-0.385890377449964</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.748751309494428</v>
+        <v>2.764706019460629</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.706954169045941</v>
+        <v>-4.678030099515338</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.113174555371895</v>
+        <v>1.124744183184137</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4149512671887724</v>
+        <v>-0.3883600839117701</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.747341886990756</v>
+        <v>2.763296596956958</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.775324355369952</v>
+        <v>-4.746400285839348</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.096833403316994</v>
+        <v>1.108403031129235</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4056755681525575</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.763914228887187</v>
+        <v>2.779868938853388</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.653907925743475</v>
+        <v>-4.624983856212872</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.135836683799475</v>
+        <v>1.147406311611717</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4056755681525575</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.754350937519078</v>
+        <v>2.77030564748528</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.031299837586259</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.620066073187471</v>
+        <v>-4.592160035905381</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.182916983997523</v>
+        <v>0.9852454047751</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4056755681525575</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.787894496694725</v>
+        <v>2.595015212525666</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.035867069578047</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.444591813395002</v>
+        <v>-4.416685776112912</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.257673919906299</v>
+        <v>1.060002340683875</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4056755681525575</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.792461728686512</v>
+        <v>2.599582444517454</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.035878543464844</v>
+        <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.555528066036251</v>
+        <v>-4.527622028754161</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213310892736597</v>
+        <v>1.015639313514173</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4056755681525575</v>
+        <v>-0.3790843848755552</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.79247320257331</v>
+        <v>2.599593918404252</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.03900992868475</v>
+        <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.758554643579484</v>
+        <v>-4.730648606297394</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.135231646939209</v>
+        <v>0.9375600677167855</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6087021456957908</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.673788641267275</v>
+        <v>2.480909357098217</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.049182315116882</v>
+        <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.600629044644191</v>
+        <v>-4.572723007362101</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.208574272945458</v>
+        <v>1.010902693723035</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6087021456957908</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.683961027699408</v>
+        <v>2.49108174353035</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.044128585690742</v>
+        <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.74895029845532</v>
+        <v>-4.72104426117323</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.144192041994867</v>
+        <v>0.9465204627724439</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6087021456957908</v>
+        <v>-0.5821109624187886</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.678907298273268</v>
+        <v>2.48602801410421</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.035904361135268</v>
+        <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.75013338310638</v>
+        <v>-4.72222734582429</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.135494583578968</v>
+        <v>0.9378230043565452</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6143451941623024</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.667297244637887</v>
+        <v>2.474417960468829</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.036456234168369</v>
+        <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.627005676112297</v>
+        <v>-4.599099638830207</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.185297539409703</v>
+        <v>0.9876259601872799</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6143451941623024</v>
+        <v>-0.5877540108853001</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.667849117670988</v>
+        <v>2.47496983350193</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.965728926059735</v>
+        <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.534195194661438</v>
+        <v>-4.506289157379348</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.151694423881413</v>
+        <v>0.9540228446589896</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.521534712711443</v>
+        <v>-0.4949435294344408</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.65280809843287</v>
+        <v>2.459928814263812</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.967602401984336</v>
+        <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.485632142440408</v>
+        <v>-4.457726105158318</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.172993120694426</v>
+        <v>0.9753215414720022</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4729716604904128</v>
+        <v>-0.4463804772134106</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.683819405690088</v>
+        <v>2.490940121521031</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.962678110496059</v>
+        <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.372960924204158</v>
+        <v>-4.345054886922068</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.213137316500648</v>
+        <v>1.015465737278225</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3603004422541626</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.746497845143562</v>
+        <v>2.553618560974503</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.968169406326726</v>
+        <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.260583923021485</v>
+        <v>-4.232677885739395</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.263579412804385</v>
+        <v>1.065907833581962</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3603004422541626</v>
+        <v>-0.3337092589771604</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.751989140974229</v>
+        <v>2.559109856805171</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.979666608095265</v>
+        <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.458818491908215</v>
+        <v>-4.430912454626125</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.195782787018232</v>
+        <v>0.9981112077958085</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5585350111408932</v>
+        <v>-0.5319438278638909</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.64454560141073</v>
+        <v>2.451666317241671</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.818022328095918</v>
+        <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.541819772933494</v>
+        <v>-4.513913735651404</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.000937994608774</v>
+        <v>0.8032664153863502</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.577105895668067</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.471758790695079</v>
+        <v>2.278879506526021</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.938171988815124</v>
+        <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.382625500876918</v>
+        <v>-4.354719463594828</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.18476536415061</v>
+        <v>0.9870937849281864</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.577105895668067</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.591908451414284</v>
+        <v>2.399029167245226</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.952685014917447</v>
+        <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.469224083858021</v>
+        <v>-4.441318046575931</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.164638957060492</v>
+        <v>0.9669673778380683</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.577105895668067</v>
+        <v>-0.5505147123910648</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.606421477516607</v>
+        <v>2.413542193347549</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383429</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.950104456259816</v>
+        <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.43084042129987</v>
+        <v>-4.402934384017779</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.177411863426121</v>
+        <v>0.9797402842036975</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5387222331099158</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.626871116393867</v>
+        <v>2.433991832224809</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.748888891187271</v>
+        <v>3.748888891187272</v>
       </c>
       <c r="C1955" t="n">
-        <v>3.031417980059448</v>
+        <v>2.822583985924189</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.43084042129987</v>
+        <v>-4.402934384017779</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.177411863426121</v>
+        <v>0.9797402842036975</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5387222331099158</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.024481777045816</v>
+        <v>2.815647782910557</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.748888891187272</v>
+        <v>3.748888891187271</v>
       </c>
       <c r="C1955" t="n">
         <v>2.822583985924189</v>

--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-37.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>115.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>441.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.9%</t>
+          <t>-605.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-84.1%</t>
+          <t>-240.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.2%</t>
+          <t>-280.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-159.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-275.2%</t>
+          <t>-256.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-191.6%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-11.2939253975352</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.352190070284593</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84393679159892</v>
+        <v>-11.0266835966668</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174029188409456</v>
+        <v>-1.247127910436607</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.72063086312071</v>
+        <v>-10.90337766818858</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.125007131991629</v>
+        <v>-1.198105854018781</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.006849454888072</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.69667732214475</v>
+        <v>-10.87942412721263</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.114757209455753</v>
+        <v>-1.187855931482904</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.982895913912114</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.43261738382195</v>
+        <v>-10.61536418888983</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.022393550288386</v>
+        <v>-1.095492272315537</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.718835975589318</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.725537760317113</v>
+        <v>-9.908284565384992</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7423487345467517</v>
+        <v>-0.8154474565739034</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.718835975589318</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.685353461950923</v>
+        <v>-9.868100267018802</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7259313913124341</v>
+        <v>-0.7990301133395858</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.678651677223127</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.605283666413118</v>
+        <v>-9.788030471480997</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6945366518765557</v>
+        <v>-0.767635373903707</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.598581881685323</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.371802444183519</v>
+        <v>-9.554549249251398</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5932197341468632</v>
+        <v>-0.666318456174015</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.365100659455724</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.192093914039646</v>
+        <v>-9.374840719107524</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5242285324022733</v>
+        <v>-0.5973272544294246</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.307929155293028</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.059818440408758</v>
+        <v>-9.242565245476637</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4759508562028913</v>
+        <v>-0.5490495782300426</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.175653681662142</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.869218765735605</v>
+        <v>-9.051965570803484</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.396895925645993</v>
+        <v>-0.4699946476731447</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.985054006988989</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.620218967052024</v>
+        <v>-8.802965772119903</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2843896649489017</v>
+        <v>-0.3574883869760535</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.985054006988989</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.725808956825128</v>
+        <v>-8.908555761893007</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4546015904573624</v>
+        <v>-0.5277003124845141</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.090643996762093</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.744543858943725</v>
+        <v>-8.927290664011604</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4135512094277147</v>
+        <v>-0.4866499314548665</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.090643996762093</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.596603817536126</v>
+        <v>-8.779350622604005</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4742541155528426</v>
+        <v>-0.5473528375799943</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.070323080853536</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.572375181147153</v>
+        <v>-8.755121986215032</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4732766472507319</v>
+        <v>-0.5463753692778832</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.046094444464564</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.528826774376462</v>
+        <v>-8.711573579444341</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4628178966375485</v>
+        <v>-0.5359166186647002</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.046094444464564</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.286678380922604</v>
+        <v>-8.469425185990483</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3514961848748621</v>
+        <v>-0.4245949069020138</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.046094444464564</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.223449009154256</v>
+        <v>-8.406195814222135</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3316723157083281</v>
+        <v>-0.4047710377354798</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.046094444464564</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.100157874337127</v>
+        <v>-8.282904679405005</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2848577677708994</v>
+        <v>-0.3579564897980507</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.922803309647434</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.079008675433684</v>
+        <v>-8.261755480501563</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2686971099721971</v>
+        <v>-0.3417958319993488</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.90165411074399</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.83524323345024</v>
+        <v>-8.017990038518118</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1754102248317686</v>
+        <v>-0.2485089468589199</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.90165411074399</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.57121516625698</v>
+        <v>-7.753961971324857</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.06767468403444887</v>
+        <v>-0.1407734060615997</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.699788711928037</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.321364772307906</v>
+        <v>-7.504111577375783</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.02500754852888321</v>
+        <v>-0.04809117349826764</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.699788711928037</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.145472679840474</v>
+        <v>-7.328219484908351</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.09896350903650486</v>
+        <v>0.02586478700935402</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.699788711928037</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.97402621681801</v>
+        <v>-7.156773021885887</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1808696003000438</v>
+        <v>0.107770878272893</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.528342248905573</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.748993217149187</v>
+        <v>-6.931740022217064</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2699032777838699</v>
+        <v>0.1968045557567191</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.30330924923675</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353075</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.53435883951278</v>
+        <v>-6.717105644580657</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3604518298927499</v>
+        <v>0.2873531078655991</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.088674871600344</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544784</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.267758482538428</v>
+        <v>-6.616964544810029</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4482862314662861</v>
+        <v>0.3086038065576457</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.088674871600344</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.027327985733568</v>
+        <v>-6.376534048005169</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5462015068131079</v>
+        <v>0.4065190819044675</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8482443747954833</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.784537178084123</v>
+        <v>-6.133743240355724</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6472471437077063</v>
+        <v>0.507564718799066</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8482443747954833</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.668597328458937</v>
+        <v>-6.017803390730538</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6943016674751203</v>
+        <v>0.55461924256648</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7714226437793594</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.425941740035775</v>
+        <v>-5.775147802307375</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.788361974064379</v>
+        <v>0.6486795491557391</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7714226437793594</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.205920941998764</v>
+        <v>-5.555127004270364</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8779493302897974</v>
+        <v>0.7382669053811575</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6302027987113792</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.006672312093955</v>
+        <v>-5.355878374365555</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9735429650535443</v>
+        <v>0.8338605401449044</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6302027987113792</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.847157208574585</v>
+        <v>-5.196363270846185</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.038494850901594</v>
+        <v>0.8988124259929542</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4706876951920093</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.702485063474848</v>
+        <v>-5.051691125746448</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.106451811502929</v>
+        <v>0.9667693865942888</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3260155500922718</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.76235989083254</v>
+        <v>-5.11156595310414</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.068539371961278</v>
+        <v>0.9288569470526378</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.385890377449964</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.675560393053532</v>
+        <v>-5.024766455325132</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.125659664395447</v>
+        <v>0.9859772394868074</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.385890377449964</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.678030099515338</v>
+        <v>-5.027236161786938</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.124744183184137</v>
+        <v>0.985061758275497</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3883600839117701</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.746400285839348</v>
+        <v>-5.095606348110948</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.108403031129235</v>
+        <v>0.9687206062205949</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3790843848755552</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.624983856212872</v>
+        <v>-4.974189918484472</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.147406311611717</v>
+        <v>1.007723886703077</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3790843848755552</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.592160035905381</v>
+        <v>-5.005183077813177</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9852454047751</v>
+        <v>0.8200361880119815</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3790843848755552</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.416685776112912</v>
+        <v>-4.829708818020707</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.060002340683875</v>
+        <v>0.8947931239207572</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3790843848755552</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.527622028754161</v>
+        <v>-4.940645070661956</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.015639313514173</v>
+        <v>0.850430096751055</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3790843848755552</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.730648606297394</v>
+        <v>-5.143671648205189</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9375600677167855</v>
+        <v>0.7723508509536674</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.5821109624187886</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.572723007362101</v>
+        <v>-4.985746049269896</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.010902693723035</v>
+        <v>0.8456934769599169</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.5821109624187886</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.72104426117323</v>
+        <v>-5.134067303081025</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9465204627724439</v>
+        <v>0.7813112460093259</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.5821109624187886</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.72222734582429</v>
+        <v>-5.135250387732086</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9378230043565452</v>
+        <v>0.7726137875934271</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.5877540108853001</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.599099638830207</v>
+        <v>-5.012122680738003</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9876259601872799</v>
+        <v>0.8224167434241618</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.5877540108853001</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.506289157379348</v>
+        <v>-4.919312199287143</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9540228446589896</v>
+        <v>0.7888136278958713</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.4949435294344408</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.457726105158318</v>
+        <v>-4.870749147066113</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9753215414720022</v>
+        <v>0.8101123247088842</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4463804772134106</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.345054886922068</v>
+        <v>-4.758077928829863</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.015465737278225</v>
+        <v>0.8502565205151071</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3337092589771604</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.232677885739395</v>
+        <v>-4.64570092764719</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.065907833581962</v>
+        <v>0.9006986168188436</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3337092589771604</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.430912454626125</v>
+        <v>-4.843935496533921</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9981112077958085</v>
+        <v>0.8329019910326902</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5319438278638909</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.513913735651404</v>
+        <v>-4.9269367775592</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8032664153863502</v>
+        <v>0.638057198623232</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5505147123910648</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.354719463594828</v>
+        <v>-4.767742505502623</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9870937849281864</v>
+        <v>0.8218845681650684</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5505147123910648</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.441318046575931</v>
+        <v>-4.854341088483726</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9669673778380683</v>
+        <v>0.8017581610749502</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5505147123910648</v>
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383429</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.402934384017779</v>
+        <v>-4.625995570139646</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9797402842036975</v>
+        <v>0.8905158097549508</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.3221691940469847</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.433991832224809</v>
+        <v>2.547968945696366</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.748888891187271</v>
+        <v>3.422475410749803</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.822583985924189</v>
+        <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.402934384017779</v>
+        <v>-4.442293029115106</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9797402842036975</v>
+        <v>0.960725855010069</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5121310498329136</v>
+        <v>-0.3221691940469847</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.815647782910557</v>
+        <v>2.544697974541668</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240505.xlsx
+++ b/tame_output/ON/bt/strategyON_20240505.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.0%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.1%</t>
+          <t>440.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-605.8%</t>
+          <t>-607.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-240.9%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.1%</t>
+          <t>-280.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.2%</t>
+          <t>-275.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-191.6%</t>
+          <t>-203.0%</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.2939253975352</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.352190070284593</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.0266835966668</v>
+        <v>-10.84393679159892</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.247127910436607</v>
+        <v>-1.174029188409456</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.90337766818858</v>
+        <v>-10.72063086312071</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.198105854018781</v>
+        <v>-1.125007131991629</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.006849454888072</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.87942412721263</v>
+        <v>-10.69667732214475</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.187855931482904</v>
+        <v>-1.114757209455753</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.982895913912114</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.61536418888983</v>
+        <v>-10.43261738382195</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.095492272315537</v>
+        <v>-1.022393550288386</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.718835975589318</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.908284565384992</v>
+        <v>-9.725537760317113</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8154474565739034</v>
+        <v>-0.7423487345467517</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.718835975589318</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.868100267018802</v>
+        <v>-9.685353461950923</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7990301133395858</v>
+        <v>-0.7259313913124341</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.678651677223127</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.788030471480997</v>
+        <v>-9.605283666413118</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.767635373903707</v>
+        <v>-0.6945366518765557</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.598581881685323</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.554549249251398</v>
+        <v>-9.371802444183519</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.666318456174015</v>
+        <v>-0.5932197341468632</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.365100659455724</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.374840719107524</v>
+        <v>-9.192093914039646</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5973272544294246</v>
+        <v>-0.5242285324022733</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.307929155293028</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.242565245476637</v>
+        <v>-9.059818440408758</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5490495782300426</v>
+        <v>-0.4759508562028913</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.175653681662142</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.051965570803484</v>
+        <v>-8.869218765735605</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4699946476731447</v>
+        <v>-0.396895925645993</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.985054006988989</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.802965772119903</v>
+        <v>-8.620218967052024</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3574883869760535</v>
+        <v>-0.2843896649489017</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.985054006988989</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.908555761893007</v>
+        <v>-8.725808956825128</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5277003124845141</v>
+        <v>-0.4546015904573624</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.090643996762093</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.927290664011604</v>
+        <v>-8.744543858943725</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4866499314548665</v>
+        <v>-0.4135512094277147</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.090643996762093</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.779350622604005</v>
+        <v>-8.596603817536126</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5473528375799943</v>
+        <v>-0.4742541155528426</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.070323080853536</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.755121986215032</v>
+        <v>-8.572375181147153</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5463753692778832</v>
+        <v>-0.4732766472507319</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.046094444464564</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.711573579444341</v>
+        <v>-8.528826774376462</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5359166186647002</v>
+        <v>-0.4628178966375485</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.046094444464564</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.469425185990483</v>
+        <v>-8.286678380922604</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4245949069020138</v>
+        <v>-0.3514961848748621</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.046094444464564</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.406195814222135</v>
+        <v>-8.223449009154256</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.4047710377354798</v>
+        <v>-0.3316723157083281</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.046094444464564</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.282904679405005</v>
+        <v>-8.100157874337127</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3579564897980507</v>
+        <v>-0.2848577677708994</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.922803309647434</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.261755480501563</v>
+        <v>-8.079008675433684</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3417958319993488</v>
+        <v>-0.2686971099721971</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.90165411074399</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.017990038518118</v>
+        <v>-7.83524323345024</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2485089468589199</v>
+        <v>-0.1754102248317686</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.90165411074399</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.753961971324857</v>
+        <v>-7.57121516625698</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1407734060615997</v>
+        <v>-0.06767468403444887</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.699788711928037</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.504111577375783</v>
+        <v>-7.321364772307906</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.04809117349826764</v>
+        <v>0.02500754852888321</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.699788711928037</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.328219484908351</v>
+        <v>-7.145472679840474</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.02586478700935402</v>
+        <v>0.09896350903650486</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.699788711928037</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.156773021885887</v>
+        <v>-6.97402621681801</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.107770878272893</v>
+        <v>0.1808696003000438</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.528342248905573</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.931740022217064</v>
+        <v>-6.748993217149187</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.1968045557567191</v>
+        <v>0.2699032777838699</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.30330924923675</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.717105644580657</v>
+        <v>-6.53435883951278</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2873531078655991</v>
+        <v>0.3604518298927499</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.088674871600344</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.616964544810029</v>
+        <v>-6.441358798306882</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3086038065576457</v>
+        <v>0.3788461051589049</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.088674871600344</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.376534048005169</v>
+        <v>-6.200928301502022</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4065190819044675</v>
+        <v>0.4767613805057263</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8482443747954833</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.133743240355724</v>
+        <v>-5.958137493852576</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.507564718799066</v>
+        <v>0.5778070174003247</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8482443747954833</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.017803390730538</v>
+        <v>-5.842197644227391</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.55461924256648</v>
+        <v>0.6248615411677387</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7714226437793594</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.775147802307375</v>
+        <v>-5.599542055804228</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6486795491557391</v>
+        <v>0.7189218477569974</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7714226437793594</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.555127004270364</v>
+        <v>-5.379521257767218</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7382669053811575</v>
+        <v>0.8085092039824158</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6302027987113792</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.355878374365555</v>
+        <v>-5.180272627862409</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8338605401449044</v>
+        <v>0.9041028387461627</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6302027987113792</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.196363270846185</v>
+        <v>-5.020757524343039</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8988124259929542</v>
+        <v>0.9690547245942125</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4706876951920093</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.051691125746448</v>
+        <v>-4.876085379243301</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9667693865942888</v>
+        <v>1.037011685195548</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3260155500922718</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.11156595310414</v>
+        <v>-4.935960206600994</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9288569470526378</v>
+        <v>0.9990992456538963</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.385890377449964</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.024766455325132</v>
+        <v>-4.849160708821985</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9859772394868074</v>
+        <v>1.056219538088066</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.385890377449964</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.027236161786938</v>
+        <v>-4.851630415283791</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.985061758275497</v>
+        <v>1.055304056876756</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.3883600839117701</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.095606348110948</v>
+        <v>-4.920000601607802</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9687206062205949</v>
+        <v>1.038962904821853</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.3790843848755552</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.974189918484472</v>
+        <v>-4.798584171981325</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.007723886703077</v>
+        <v>1.077966185304335</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.3790843848755552</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.005183077813177</v>
+        <v>-4.829577331310031</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8200361880119815</v>
+        <v>0.89027848661324</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.3790843848755552</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.829708818020707</v>
+        <v>-4.654103071517561</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8947931239207572</v>
+        <v>0.9650354225220157</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.3790843848755552</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.940645070661956</v>
+        <v>-4.76503932415881</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.850430096751055</v>
+        <v>0.9206723953523137</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.3790843848755552</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.143671648205189</v>
+        <v>-4.968065901702043</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7723508509536674</v>
+        <v>0.8425931495549259</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.5821109624187886</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.985746049269896</v>
+        <v>-4.81014030276675</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8456934769599169</v>
+        <v>0.9159357755611754</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.5821109624187886</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.134067303081025</v>
+        <v>-4.958461556577879</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7813112460093259</v>
+        <v>0.8515535446105842</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.5821109624187886</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.135250387732086</v>
+        <v>-4.959644641228939</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7726137875934271</v>
+        <v>0.8428560861946857</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.5877540108853001</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.012122680738003</v>
+        <v>-4.836516934234856</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8224167434241618</v>
+        <v>0.8926590420254203</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.5877540108853001</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.919312199287143</v>
+        <v>-4.743706452783996</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7888136278958713</v>
+        <v>0.8590559264971298</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.4949435294344408</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.870749147066113</v>
+        <v>-4.695143400562967</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8101123247088842</v>
+        <v>0.8803546233101427</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4463804772134106</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.758077928829863</v>
+        <v>-4.582472182326716</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8502565205151071</v>
+        <v>0.9204988191163657</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3337092589771604</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.64570092764719</v>
+        <v>-4.470095181144043</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9006986168188436</v>
+        <v>0.9709409154201021</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3337092589771604</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.843935496533921</v>
+        <v>-4.668329750030774</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8329019910326902</v>
+        <v>0.903144289633949</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5319438278638909</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.9269367775592</v>
+        <v>-4.751331031056053</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.638057198623232</v>
+        <v>0.7082994972244907</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5505147123910648</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.767742505502623</v>
+        <v>-4.592136758999477</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8218845681650684</v>
+        <v>0.8921268667663269</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5505147123910648</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.854341088483726</v>
+        <v>-4.678735341980579</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8017581610749502</v>
+        <v>0.8720004596762088</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5505147123910648</v>
@@ -46493,16 +46493,16 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.625995570139646</v>
+        <v>-4.640351679422428</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8905158097549508</v>
+        <v>0.8847733660418378</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3221691940469847</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.547968945696366</v>
+        <v>2.433991832224809</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.442293029115106</v>
+        <v>-4.459103374188722</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.960725855010069</v>
+        <v>0.9540017169806225</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3221691940469847</v>
+        <v>-0.5121310498329136</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.544697974541668</v>
+        <v>2.430720861070111</v>
       </c>
     </row>
   </sheetData>
